--- a/data/split/val.xlsx
+++ b/data/split/val.xlsx
@@ -550,8 +550,10 @@
       <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -686,8 +688,10 @@
       <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
-        <v>4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -822,8 +826,10 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -1027,8 +1033,10 @@
       <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
-        <v>5</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1094,8 +1102,10 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>5</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1161,8 +1171,10 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
-        <v>5</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1228,8 +1240,10 @@
       <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>5</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1433,8 +1447,10 @@
       <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
-        <v>4</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -1500,8 +1516,10 @@
       <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>5</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N16" t="n">
         <v>2</v>
@@ -1567,8 +1585,10 @@
       <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1634,8 +1654,10 @@
       <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M18" t="n">
-        <v>4</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1701,8 +1723,10 @@
       <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" t="n">
-        <v>4</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -1768,8 +1792,10 @@
       <c r="L20" t="n">
         <v>5</v>
       </c>
-      <c r="M20" t="n">
-        <v>4</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1835,8 +1861,10 @@
       <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
-        <v>5</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -1902,8 +1930,10 @@
       <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>4</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2038,8 +2068,10 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="n">
-        <v>1</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2174,8 +2206,10 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="n">
-        <v>4</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2241,8 +2275,10 @@
       <c r="L27" t="n">
         <v>4</v>
       </c>
-      <c r="M27" t="n">
-        <v>4</v>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N27" t="n">
         <v>2</v>
@@ -2377,8 +2413,10 @@
       <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
-        <v>4</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N29" t="n">
         <v>1</v>
@@ -2444,8 +2482,10 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N30" t="n">
         <v>1</v>
@@ -2580,8 +2620,10 @@
       <c r="L32" t="n">
         <v>4</v>
       </c>
-      <c r="M32" t="n">
-        <v>4</v>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N32" t="n">
         <v>2</v>
@@ -2647,8 +2689,10 @@
       <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>4</v>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N33" t="n">
         <v>2</v>
@@ -2714,8 +2758,10 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>1</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -2850,8 +2896,10 @@
       <c r="L36" t="n">
         <v>5</v>
       </c>
-      <c r="M36" t="n">
-        <v>4</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -2917,8 +2965,10 @@
       <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="M37" t="n">
-        <v>5</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N37" t="n">
         <v>2</v>
@@ -3260,8 +3310,10 @@
       <c r="L42" t="n">
         <v>3</v>
       </c>
-      <c r="M42" t="n">
-        <v>4</v>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N42" t="n">
         <v>2</v>
@@ -3327,8 +3379,10 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="n">
-        <v>3</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3463,8 +3517,10 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -3530,8 +3586,10 @@
       <c r="L46" t="n">
         <v>4</v>
       </c>
-      <c r="M46" t="n">
-        <v>3</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N46" t="n">
         <v>1</v>
@@ -3804,8 +3862,10 @@
       <c r="L50" t="n">
         <v>5</v>
       </c>
-      <c r="M50" t="n">
-        <v>1</v>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N50" t="n">
         <v>2</v>
@@ -3871,8 +3931,10 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="n">
-        <v>4</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N51" t="n">
         <v>1</v>
@@ -4007,8 +4069,10 @@
       <c r="L53" t="n">
         <v>4</v>
       </c>
-      <c r="M53" t="n">
-        <v>4</v>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N53" t="n">
         <v>2</v>
@@ -4143,8 +4207,10 @@
       <c r="L55" t="n">
         <v>4</v>
       </c>
-      <c r="M55" t="n">
-        <v>4</v>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N55" t="n">
         <v>2</v>
@@ -4279,8 +4345,10 @@
       <c r="L57" t="n">
         <v>3</v>
       </c>
-      <c r="M57" t="n">
-        <v>1</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -4346,8 +4414,10 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="n">
-        <v>5</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N58" t="n">
         <v>2</v>
@@ -4413,8 +4483,10 @@
       <c r="L59" t="n">
         <v>4</v>
       </c>
-      <c r="M59" t="n">
-        <v>5</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N59" t="n">
         <v>2</v>
@@ -4480,8 +4552,10 @@
       <c r="L60" t="n">
         <v>4</v>
       </c>
-      <c r="M60" t="n">
-        <v>2</v>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N60" t="n">
         <v>1</v>
@@ -4616,8 +4690,10 @@
       <c r="L62" t="n">
         <v>4</v>
       </c>
-      <c r="M62" t="n">
-        <v>4</v>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N62" t="n">
         <v>2</v>
@@ -4683,8 +4759,10 @@
       <c r="L63" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="n">
-        <v>4</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -4750,8 +4828,10 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="n">
-        <v>4</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -4955,8 +5035,10 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="n">
-        <v>5</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5022,8 +5104,10 @@
       <c r="L68" t="n">
         <v>5</v>
       </c>
-      <c r="M68" t="n">
-        <v>5</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N68" t="n">
         <v>2</v>
@@ -5089,8 +5173,10 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="n">
-        <v>4</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -5156,8 +5242,10 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="n">
-        <v>5</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -5223,8 +5311,10 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="n">
-        <v>5</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -5359,8 +5449,10 @@
       <c r="L73" t="n">
         <v>4</v>
       </c>
-      <c r="M73" t="n">
-        <v>4</v>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N73" t="n">
         <v>1</v>
@@ -5495,8 +5587,10 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="n">
-        <v>4</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N75" t="n">
         <v>2</v>
@@ -5562,8 +5656,10 @@
       <c r="L76" t="n">
         <v>3</v>
       </c>
-      <c r="M76" t="n">
-        <v>4</v>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N76" t="n">
         <v>2</v>
@@ -5629,8 +5725,10 @@
       <c r="L77" t="n">
         <v>4</v>
       </c>
-      <c r="M77" t="n">
-        <v>4</v>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N77" t="n">
         <v>2</v>
@@ -5696,8 +5794,10 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="n">
-        <v>4</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -5763,8 +5863,10 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
-        <v>5</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -5830,8 +5932,10 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -5897,8 +6001,10 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="n">
-        <v>5</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -5964,8 +6070,10 @@
       <c r="L82" t="n">
         <v>4</v>
       </c>
-      <c r="M82" t="n">
-        <v>4</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -6031,8 +6139,10 @@
       <c r="L83" t="n">
         <v>3</v>
       </c>
-      <c r="M83" t="n">
-        <v>1</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N83" t="n">
         <v>2</v>
@@ -6167,8 +6277,10 @@
       <c r="L85" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="n">
-        <v>4</v>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N85" t="n">
         <v>2</v>
@@ -6234,8 +6346,10 @@
       <c r="L86" t="n">
         <v>4</v>
       </c>
-      <c r="M86" t="n">
-        <v>4</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -6301,8 +6415,10 @@
       <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="M87" t="n">
-        <v>4</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N87" t="n">
         <v>2</v>
@@ -6368,8 +6484,10 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="n">
-        <v>1</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -6435,8 +6553,10 @@
       <c r="L89" t="n">
         <v>4</v>
       </c>
-      <c r="M89" t="n">
-        <v>5</v>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N89" t="n">
         <v>2</v>
@@ -6571,8 +6691,10 @@
       <c r="L91" t="n">
         <v>5</v>
       </c>
-      <c r="M91" t="n">
-        <v>5</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -6638,8 +6760,10 @@
       <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="n">
-        <v>4</v>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N92" t="n">
         <v>2</v>
@@ -6705,8 +6829,10 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
-      <c r="M93" t="n">
-        <v>4</v>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N93" t="n">
         <v>2</v>
@@ -6772,8 +6898,10 @@
       <c r="L94" t="n">
         <v>2</v>
       </c>
-      <c r="M94" t="n">
-        <v>3</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -6839,8 +6967,10 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="n">
-        <v>5</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -6975,8 +7105,10 @@
       <c r="L97" t="n">
         <v>3</v>
       </c>
-      <c r="M97" t="n">
-        <v>4</v>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N97" t="n">
         <v>2</v>
@@ -7042,8 +7174,10 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="n">
-        <v>4</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -7109,8 +7243,10 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="n">
-        <v>1</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -7176,8 +7312,10 @@
       <c r="L100" t="n">
         <v>5</v>
       </c>
-      <c r="M100" t="n">
-        <v>4</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -7243,8 +7381,10 @@
       <c r="L101" t="n">
         <v>3</v>
       </c>
-      <c r="M101" t="n">
-        <v>1</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -7310,8 +7450,10 @@
       <c r="L102" t="n">
         <v>5</v>
       </c>
-      <c r="M102" t="n">
-        <v>4</v>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N102" t="n">
         <v>2</v>
@@ -7515,8 +7657,10 @@
       <c r="L105" t="n">
         <v>5</v>
       </c>
-      <c r="M105" t="n">
-        <v>5</v>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -7582,8 +7726,10 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -7649,8 +7795,10 @@
       <c r="L107" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="n">
-        <v>4</v>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -7716,8 +7864,10 @@
       <c r="L108" t="n">
         <v>2</v>
       </c>
-      <c r="M108" t="n">
-        <v>4</v>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -7783,8 +7933,10 @@
       <c r="L109" t="n">
         <v>4</v>
       </c>
-      <c r="M109" t="n">
-        <v>4</v>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -7850,8 +8002,10 @@
       <c r="L110" t="n">
         <v>4</v>
       </c>
-      <c r="M110" t="n">
-        <v>5</v>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N110" t="n">
         <v>1</v>
@@ -7917,8 +8071,10 @@
       <c r="L111" t="n">
         <v>3</v>
       </c>
-      <c r="M111" t="n">
-        <v>4</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -7984,8 +8140,10 @@
       <c r="L112" t="n">
         <v>1</v>
       </c>
-      <c r="M112" t="n">
-        <v>4</v>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N112" t="n">
         <v>3</v>
@@ -8051,8 +8209,10 @@
       <c r="L113" t="n">
         <v>5</v>
       </c>
-      <c r="M113" t="n">
-        <v>1</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -8187,8 +8347,10 @@
       <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>4</v>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -8323,8 +8485,10 @@
       <c r="L117" t="n">
         <v>4</v>
       </c>
-      <c r="M117" t="n">
-        <v>5</v>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N117" t="n">
         <v>2</v>
@@ -8528,8 +8692,10 @@
       <c r="L120" t="n">
         <v>4</v>
       </c>
-      <c r="M120" t="n">
-        <v>4</v>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N120" t="n">
         <v>2</v>
@@ -8595,8 +8761,10 @@
       <c r="L121" t="n">
         <v>4</v>
       </c>
-      <c r="M121" t="n">
-        <v>4</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -8662,8 +8830,10 @@
       <c r="L122" t="n">
         <v>2</v>
       </c>
-      <c r="M122" t="n">
-        <v>4</v>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N122" t="n">
         <v>2</v>
@@ -8729,8 +8899,10 @@
       <c r="L123" t="n">
         <v>4</v>
       </c>
-      <c r="M123" t="n">
-        <v>4</v>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -8865,8 +9037,10 @@
       <c r="L125" t="n">
         <v>5</v>
       </c>
-      <c r="M125" t="n">
-        <v>1</v>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N125" t="n">
         <v>3</v>
@@ -8932,8 +9106,10 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="n">
-        <v>4</v>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -9137,8 +9313,10 @@
       <c r="L129" t="n">
         <v>4</v>
       </c>
-      <c r="M129" t="n">
-        <v>4</v>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -9204,8 +9382,10 @@
       <c r="L130" t="n">
         <v>2</v>
       </c>
-      <c r="M130" t="n">
-        <v>5</v>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -9271,8 +9451,10 @@
       <c r="L131" t="n">
         <v>4</v>
       </c>
-      <c r="M131" t="n">
-        <v>4</v>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N131" t="n">
         <v>2</v>
@@ -9338,8 +9520,10 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="n">
-        <v>4</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -9543,8 +9727,10 @@
       <c r="L135" t="n">
         <v>4</v>
       </c>
-      <c r="M135" t="n">
-        <v>4</v>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N135" t="n">
         <v>2</v>
@@ -9610,8 +9796,10 @@
       <c r="L136" t="n">
         <v>4</v>
       </c>
-      <c r="M136" t="n">
-        <v>5</v>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -9677,8 +9865,10 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="n">
-        <v>1</v>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N137" t="n">
         <v>1</v>
@@ -9813,8 +10003,10 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="n">
-        <v>4</v>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -9880,8 +10072,10 @@
       <c r="L140" t="n">
         <v>3</v>
       </c>
-      <c r="M140" t="n">
-        <v>5</v>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N140" t="n">
         <v>1</v>
@@ -9947,8 +10141,10 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="n">
-        <v>1</v>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N141" t="n">
         <v>2</v>
@@ -10083,8 +10279,10 @@
       <c r="L143" t="n">
         <v>5</v>
       </c>
-      <c r="M143" t="n">
-        <v>1</v>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N143" t="n">
         <v>2</v>
@@ -10150,8 +10348,10 @@
       <c r="L144" t="n">
         <v>4</v>
       </c>
-      <c r="M144" t="n">
-        <v>5</v>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N144" t="n">
         <v>2</v>
@@ -10217,8 +10417,10 @@
       <c r="L145" t="n">
         <v>3</v>
       </c>
-      <c r="M145" t="n">
-        <v>5</v>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N145" t="n">
         <v>2</v>
@@ -10353,8 +10555,10 @@
       <c r="L147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="n">
-        <v>5</v>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N147" t="n">
         <v>2</v>
@@ -10420,8 +10624,10 @@
       <c r="L148" t="n">
         <v>2</v>
       </c>
-      <c r="M148" t="n">
-        <v>4</v>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -10487,8 +10693,10 @@
       <c r="L149" t="n">
         <v>4</v>
       </c>
-      <c r="M149" t="n">
-        <v>4</v>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N149" t="n">
         <v>2</v>
@@ -10554,8 +10762,10 @@
       <c r="L150" t="n">
         <v>4</v>
       </c>
-      <c r="M150" t="n">
-        <v>4</v>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N150" t="n">
         <v>1</v>
@@ -10621,8 +10831,10 @@
       <c r="L151" t="n">
         <v>4</v>
       </c>
-      <c r="M151" t="n">
-        <v>4</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N151" t="n">
         <v>2</v>
@@ -10688,8 +10900,10 @@
       <c r="L152" t="n">
         <v>5</v>
       </c>
-      <c r="M152" t="n">
-        <v>4</v>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N152" t="n">
         <v>1</v>
@@ -10755,8 +10969,10 @@
       <c r="L153" t="n">
         <v>3</v>
       </c>
-      <c r="M153" t="n">
-        <v>4</v>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N153" t="n">
         <v>1</v>
@@ -10822,8 +11038,10 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="n">
-        <v>4</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N154" t="n">
         <v>1</v>
@@ -10889,8 +11107,10 @@
       <c r="L155" t="n">
         <v>2</v>
       </c>
-      <c r="M155" t="n">
-        <v>5</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -11025,8 +11245,10 @@
       <c r="L157" t="n">
         <v>2</v>
       </c>
-      <c r="M157" t="n">
-        <v>4</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -11230,8 +11452,10 @@
       <c r="L160" t="n">
         <v>2</v>
       </c>
-      <c r="M160" t="n">
-        <v>5</v>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N160" t="n">
         <v>2</v>
@@ -11297,8 +11521,10 @@
       <c r="L161" t="n">
         <v>4</v>
       </c>
-      <c r="M161" t="n">
-        <v>4</v>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N161" t="n">
         <v>2</v>
@@ -11433,8 +11659,10 @@
       <c r="L163" t="n">
         <v>3</v>
       </c>
-      <c r="M163" t="n">
-        <v>4</v>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -11500,8 +11728,10 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="n">
-        <v>4</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -11567,8 +11797,10 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="n">
-        <v>3</v>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -11634,8 +11866,10 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="n">
-        <v>1</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -11701,8 +11935,10 @@
       <c r="L167" t="n">
         <v>4</v>
       </c>
-      <c r="M167" t="n">
-        <v>4</v>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N167" t="n">
         <v>2</v>
@@ -11768,8 +12004,10 @@
       <c r="L168" t="n">
         <v>4</v>
       </c>
-      <c r="M168" t="n">
-        <v>3</v>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N168" t="n">
         <v>1</v>
@@ -11973,8 +12211,10 @@
       <c r="L171" t="n">
         <v>2</v>
       </c>
-      <c r="M171" t="n">
-        <v>5</v>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -12040,8 +12280,10 @@
       <c r="L172" t="n">
         <v>5</v>
       </c>
-      <c r="M172" t="n">
-        <v>4</v>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N172" t="n">
         <v>1</v>
@@ -12107,8 +12349,10 @@
       <c r="L173" t="n">
         <v>4</v>
       </c>
-      <c r="M173" t="n">
-        <v>3</v>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N173" t="n">
         <v>2</v>
@@ -12174,8 +12418,10 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="n">
-        <v>4</v>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -12241,8 +12487,10 @@
       <c r="L175" t="n">
         <v>4</v>
       </c>
-      <c r="M175" t="n">
-        <v>4</v>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N175" t="n">
         <v>2</v>
@@ -12308,8 +12556,10 @@
       <c r="L176" t="n">
         <v>5</v>
       </c>
-      <c r="M176" t="n">
-        <v>4</v>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N176" t="n">
         <v>2</v>
@@ -12375,8 +12625,10 @@
       <c r="L177" t="n">
         <v>5</v>
       </c>
-      <c r="M177" t="n">
-        <v>5</v>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N177" t="n">
         <v>1</v>
@@ -12442,8 +12694,10 @@
       <c r="L178" t="n">
         <v>5</v>
       </c>
-      <c r="M178" t="n">
-        <v>5</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N178" t="n">
         <v>1</v>
@@ -12509,8 +12763,10 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="n">
-        <v>1</v>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N179" t="n">
         <v>1</v>
@@ -12645,8 +12901,10 @@
       <c r="L181" t="n">
         <v>5</v>
       </c>
-      <c r="M181" t="n">
-        <v>5</v>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -12781,8 +13039,10 @@
       <c r="L183" t="n">
         <v>5</v>
       </c>
-      <c r="M183" t="n">
-        <v>5</v>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -12848,8 +13108,10 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="n">
-        <v>5</v>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N184" t="n">
         <v>2</v>
@@ -12915,8 +13177,10 @@
       <c r="L185" t="n">
         <v>4</v>
       </c>
-      <c r="M185" t="n">
-        <v>5</v>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N185" t="n">
         <v>2</v>
@@ -12982,8 +13246,10 @@
       <c r="L186" t="n">
         <v>4</v>
       </c>
-      <c r="M186" t="n">
-        <v>5</v>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N186" t="n">
         <v>2</v>
@@ -13118,8 +13384,10 @@
       <c r="L188" t="n">
         <v>3</v>
       </c>
-      <c r="M188" t="n">
-        <v>4</v>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -13185,8 +13453,10 @@
       <c r="L189" t="n">
         <v>4</v>
       </c>
-      <c r="M189" t="n">
-        <v>5</v>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N189" t="n">
         <v>2</v>
@@ -13459,8 +13729,10 @@
       <c r="L193" t="n">
         <v>5</v>
       </c>
-      <c r="M193" t="n">
-        <v>3</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N193" t="n">
         <v>1</v>
@@ -13526,8 +13798,10 @@
       <c r="L194" t="n">
         <v>4</v>
       </c>
-      <c r="M194" t="n">
-        <v>4</v>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N194" t="n">
         <v>2</v>
@@ -13593,8 +13867,10 @@
       <c r="L195" t="n">
         <v>5</v>
       </c>
-      <c r="M195" t="n">
-        <v>4</v>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N195" t="n">
         <v>1</v>
@@ -13660,8 +13936,10 @@
       <c r="L196" t="n">
         <v>4</v>
       </c>
-      <c r="M196" t="n">
-        <v>4</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N196" t="n">
         <v>3</v>
@@ -13727,8 +14005,10 @@
       <c r="L197" t="n">
         <v>4</v>
       </c>
-      <c r="M197" t="n">
-        <v>4</v>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N197" t="n">
         <v>2</v>
@@ -13863,8 +14143,10 @@
       <c r="L199" t="n">
         <v>2</v>
       </c>
-      <c r="M199" t="n">
-        <v>4</v>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N199" t="n">
         <v>2</v>
@@ -13930,8 +14212,10 @@
       <c r="L200" t="n">
         <v>3</v>
       </c>
-      <c r="M200" t="n">
-        <v>5</v>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -13997,8 +14281,10 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
-      <c r="M201" t="n">
-        <v>4</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -14133,8 +14419,10 @@
       <c r="L203" t="n">
         <v>3</v>
       </c>
-      <c r="M203" t="n">
-        <v>1</v>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -14269,8 +14557,10 @@
       <c r="L205" t="n">
         <v>4</v>
       </c>
-      <c r="M205" t="n">
-        <v>4</v>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -14543,8 +14833,10 @@
       <c r="L209" t="n">
         <v>3</v>
       </c>
-      <c r="M209" t="n">
-        <v>5</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N209" t="n">
         <v>2</v>
@@ -14610,8 +14902,10 @@
       <c r="L210" t="n">
         <v>2</v>
       </c>
-      <c r="M210" t="n">
-        <v>5</v>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N210" t="n">
         <v>2</v>
@@ -14677,8 +14971,10 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="n">
-        <v>4</v>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -14813,8 +15109,10 @@
       <c r="L213" t="n">
         <v>2</v>
       </c>
-      <c r="M213" t="n">
-        <v>4</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N213" t="n">
         <v>3</v>
@@ -14880,8 +15178,10 @@
       <c r="L214" t="n">
         <v>5</v>
       </c>
-      <c r="M214" t="n">
-        <v>4</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -14947,8 +15247,10 @@
       <c r="L215" t="n">
         <v>5</v>
       </c>
-      <c r="M215" t="n">
-        <v>5</v>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N215" t="n">
         <v>2</v>
@@ -15152,8 +15454,10 @@
       <c r="L218" t="n">
         <v>5</v>
       </c>
-      <c r="M218" t="n">
-        <v>4</v>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N218" t="n">
         <v>2</v>
@@ -15288,8 +15592,10 @@
       <c r="L220" t="n">
         <v>4</v>
       </c>
-      <c r="M220" t="n">
-        <v>1</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -15493,8 +15799,10 @@
       <c r="L223" t="n">
         <v>5</v>
       </c>
-      <c r="M223" t="n">
-        <v>1</v>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N223" t="n">
         <v>2</v>
@@ -15560,8 +15868,10 @@
       <c r="L224" t="n">
         <v>5</v>
       </c>
-      <c r="M224" t="n">
-        <v>4</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -15627,8 +15937,10 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="n">
-        <v>5</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -15694,8 +16006,10 @@
       <c r="L226" t="n">
         <v>5</v>
       </c>
-      <c r="M226" t="n">
-        <v>1</v>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N226" t="n">
         <v>1</v>
@@ -15761,8 +16075,10 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="n">
-        <v>4</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -15897,8 +16213,10 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="n">
-        <v>4</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N229" t="n">
         <v>3</v>
@@ -15964,8 +16282,10 @@
       <c r="L230" t="n">
         <v>5</v>
       </c>
-      <c r="M230" t="n">
-        <v>5</v>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N230" t="n">
         <v>2</v>
@@ -16169,8 +16489,10 @@
       <c r="L233" t="n">
         <v>5</v>
       </c>
-      <c r="M233" t="n">
-        <v>4</v>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -16236,8 +16558,10 @@
       <c r="L234" t="n">
         <v>2</v>
       </c>
-      <c r="M234" t="n">
-        <v>4</v>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N234" t="n">
         <v>2</v>
@@ -16372,8 +16696,10 @@
       <c r="L236" t="n">
         <v>4</v>
       </c>
-      <c r="M236" t="n">
-        <v>4</v>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N236" t="n">
         <v>2</v>
@@ -16439,8 +16765,10 @@
       <c r="L237" t="n">
         <v>5</v>
       </c>
-      <c r="M237" t="n">
-        <v>5</v>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N237" t="n">
         <v>2</v>
@@ -16506,8 +16834,10 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="n">
-        <v>4</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -16573,8 +16903,10 @@
       <c r="L239" t="n">
         <v>3</v>
       </c>
-      <c r="M239" t="n">
-        <v>4</v>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N239" t="n">
         <v>3</v>
@@ -16640,8 +16972,10 @@
       <c r="L240" t="n">
         <v>5</v>
       </c>
-      <c r="M240" t="n">
-        <v>4</v>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N240" t="n">
         <v>2</v>
@@ -16707,8 +17041,10 @@
       <c r="L241" t="n">
         <v>3</v>
       </c>
-      <c r="M241" t="n">
-        <v>4</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -16774,8 +17110,10 @@
       <c r="L242" t="n">
         <v>2</v>
       </c>
-      <c r="M242" t="n">
-        <v>5</v>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N242" t="n">
         <v>2</v>
@@ -16910,8 +17248,10 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="n">
-        <v>4</v>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N244" t="n">
         <v>2</v>
@@ -16977,8 +17317,10 @@
       <c r="L245" t="n">
         <v>5</v>
       </c>
-      <c r="M245" t="n">
-        <v>4</v>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N245" t="n">
         <v>2</v>
@@ -17044,8 +17386,10 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="n">
-        <v>4</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -17111,8 +17455,10 @@
       <c r="L247" t="n">
         <v>2</v>
       </c>
-      <c r="M247" t="n">
-        <v>4</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N247" t="n">
         <v>3</v>
@@ -17316,8 +17662,10 @@
       <c r="L250" t="n">
         <v>5</v>
       </c>
-      <c r="M250" t="n">
-        <v>1</v>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N250" t="n">
         <v>2</v>
@@ -17383,8 +17731,10 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="n">
-        <v>1</v>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N251" t="n">
         <v>1</v>
@@ -17450,8 +17800,10 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="n">
-        <v>4</v>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -17655,8 +18007,10 @@
       <c r="L255" t="n">
         <v>4</v>
       </c>
-      <c r="M255" t="n">
-        <v>1</v>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N255" t="n">
         <v>2</v>
@@ -17722,8 +18076,10 @@
       <c r="L256" t="n">
         <v>4</v>
       </c>
-      <c r="M256" t="n">
-        <v>3</v>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N256" t="n">
         <v>2</v>
@@ -17789,8 +18145,10 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="n">
-        <v>4</v>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N257" t="n">
         <v>2</v>
@@ -17856,8 +18214,10 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="n">
-        <v>1</v>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N258" t="n">
         <v>1</v>
@@ -17923,8 +18283,10 @@
       <c r="L259" t="n">
         <v>2</v>
       </c>
-      <c r="M259" t="n">
-        <v>4</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N259" t="n">
         <v>2</v>
@@ -17990,8 +18352,10 @@
       <c r="L260" t="n">
         <v>5</v>
       </c>
-      <c r="M260" t="n">
-        <v>1</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -18126,8 +18490,10 @@
       <c r="L262" t="n">
         <v>2</v>
       </c>
-      <c r="M262" t="n">
-        <v>2</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -18193,8 +18559,10 @@
       <c r="L263" t="n">
         <v>1</v>
       </c>
-      <c r="M263" t="n">
-        <v>4</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N263" t="n">
         <v>3</v>
@@ -18260,8 +18628,10 @@
       <c r="L264" t="n">
         <v>3</v>
       </c>
-      <c r="M264" t="n">
-        <v>1</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -18396,8 +18766,10 @@
       <c r="L266" t="n">
         <v>4</v>
       </c>
-      <c r="M266" t="n">
-        <v>4</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -18463,8 +18835,10 @@
       <c r="L267" t="n">
         <v>4</v>
       </c>
-      <c r="M267" t="n">
-        <v>4</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -18530,8 +18904,10 @@
       <c r="L268" t="n">
         <v>5</v>
       </c>
-      <c r="M268" t="n">
-        <v>3</v>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N268" t="n">
         <v>1</v>
@@ -18597,8 +18973,10 @@
       <c r="L269" t="n">
         <v>5</v>
       </c>
-      <c r="M269" t="n">
-        <v>4</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -18664,8 +19042,10 @@
       <c r="L270" t="n">
         <v>4</v>
       </c>
-      <c r="M270" t="n">
-        <v>4</v>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N270" t="n">
         <v>2</v>
@@ -18800,8 +19180,10 @@
       <c r="L272" t="n">
         <v>4</v>
       </c>
-      <c r="M272" t="n">
-        <v>4</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -18936,8 +19318,10 @@
       <c r="L274" t="n">
         <v>2</v>
       </c>
-      <c r="M274" t="n">
-        <v>4</v>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N274" t="n">
         <v>2</v>
@@ -19003,8 +19387,10 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="n">
-        <v>4</v>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -19070,8 +19456,10 @@
       <c r="L276" t="n">
         <v>5</v>
       </c>
-      <c r="M276" t="n">
-        <v>5</v>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -19137,8 +19525,10 @@
       <c r="L277" t="n">
         <v>2</v>
       </c>
-      <c r="M277" t="n">
-        <v>5</v>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -19273,8 +19663,10 @@
       <c r="L279" t="n">
         <v>1</v>
       </c>
-      <c r="M279" t="n">
-        <v>1</v>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N279" t="n">
         <v>0</v>
@@ -19409,8 +19801,10 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="n">
-        <v>5</v>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -19476,8 +19870,10 @@
       <c r="L282" t="n">
         <v>4</v>
       </c>
-      <c r="M282" t="n">
-        <v>1</v>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -19543,8 +19939,10 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="n">
-        <v>1</v>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -19610,8 +20008,10 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="n">
-        <v>4</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N284" t="n">
         <v>2</v>
@@ -19677,8 +20077,10 @@
       <c r="L285" t="n">
         <v>4</v>
       </c>
-      <c r="M285" t="n">
-        <v>4</v>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -19744,8 +20146,10 @@
       <c r="L286" t="n">
         <v>5</v>
       </c>
-      <c r="M286" t="n">
-        <v>5</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -19811,8 +20215,10 @@
       <c r="L287" t="n">
         <v>3</v>
       </c>
-      <c r="M287" t="n">
-        <v>4</v>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -20016,8 +20422,10 @@
       <c r="L290" t="n">
         <v>4</v>
       </c>
-      <c r="M290" t="n">
-        <v>5</v>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N290" t="n">
         <v>2</v>
@@ -20083,8 +20491,10 @@
       <c r="L291" t="n">
         <v>2</v>
       </c>
-      <c r="M291" t="n">
-        <v>5</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N291" t="n">
         <v>1</v>
@@ -20219,8 +20629,10 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="n">
-        <v>4</v>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N293" t="n">
         <v>2</v>
@@ -20286,8 +20698,10 @@
       <c r="L294" t="n">
         <v>4</v>
       </c>
-      <c r="M294" t="n">
-        <v>4</v>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N294" t="n">
         <v>2</v>

--- a/data/split/val.xlsx
+++ b/data/split/val.xlsx
@@ -570,8 +570,10 @@
       <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -730,8 +732,10 @@
       <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
-        <v>4</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -890,8 +894,10 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -1131,8 +1137,10 @@
       <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="n">
-        <v>5</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1210,8 +1218,10 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>5</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1289,8 +1299,10 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
-        <v>5</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1368,8 +1380,10 @@
       <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>5</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1609,8 +1623,10 @@
       <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
-        <v>4</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -1688,8 +1704,10 @@
       <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>5</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N16" t="n">
         <v>2</v>
@@ -1767,8 +1785,10 @@
       <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1846,8 +1866,10 @@
       <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M18" t="n">
-        <v>4</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1925,8 +1947,10 @@
       <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" t="n">
-        <v>4</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -2004,8 +2028,10 @@
       <c r="L20" t="n">
         <v>5</v>
       </c>
-      <c r="M20" t="n">
-        <v>4</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -2083,8 +2109,10 @@
       <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
-        <v>5</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -2162,8 +2190,10 @@
       <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>4</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2322,8 +2352,10 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="n">
-        <v>1</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2482,8 +2514,10 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="n">
-        <v>4</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2561,8 +2595,10 @@
       <c r="L27" t="n">
         <v>4</v>
       </c>
-      <c r="M27" t="n">
-        <v>4</v>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N27" t="n">
         <v>2</v>
@@ -2721,8 +2757,10 @@
       <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
-        <v>4</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N29" t="n">
         <v>1</v>
@@ -2800,8 +2838,10 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N30" t="n">
         <v>1</v>
@@ -2960,8 +3000,10 @@
       <c r="L32" t="n">
         <v>4</v>
       </c>
-      <c r="M32" t="n">
-        <v>4</v>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N32" t="n">
         <v>2</v>
@@ -3039,8 +3081,10 @@
       <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="n">
-        <v>4</v>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N33" t="n">
         <v>2</v>
@@ -3118,8 +3162,10 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="n">
-        <v>1</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -3278,8 +3324,10 @@
       <c r="L36" t="n">
         <v>5</v>
       </c>
-      <c r="M36" t="n">
-        <v>4</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -3357,8 +3405,10 @@
       <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="M37" t="n">
-        <v>5</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N37" t="n">
         <v>2</v>
@@ -3760,8 +3810,10 @@
       <c r="L42" t="n">
         <v>3</v>
       </c>
-      <c r="M42" t="n">
-        <v>4</v>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N42" t="n">
         <v>2</v>
@@ -3839,8 +3891,10 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="n">
-        <v>3</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3999,8 +4053,10 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -4078,8 +4134,10 @@
       <c r="L46" t="n">
         <v>4</v>
       </c>
-      <c r="M46" t="n">
-        <v>3</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N46" t="n">
         <v>1</v>
@@ -4400,8 +4458,10 @@
       <c r="L50" t="n">
         <v>5</v>
       </c>
-      <c r="M50" t="n">
-        <v>1</v>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N50" t="n">
         <v>2</v>
@@ -4479,8 +4539,10 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="n">
-        <v>4</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N51" t="n">
         <v>1</v>
@@ -4639,8 +4701,10 @@
       <c r="L53" t="n">
         <v>4</v>
       </c>
-      <c r="M53" t="n">
-        <v>4</v>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N53" t="n">
         <v>2</v>
@@ -4799,8 +4863,10 @@
       <c r="L55" t="n">
         <v>4</v>
       </c>
-      <c r="M55" t="n">
-        <v>4</v>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N55" t="n">
         <v>2</v>
@@ -4959,8 +5025,10 @@
       <c r="L57" t="n">
         <v>3</v>
       </c>
-      <c r="M57" t="n">
-        <v>1</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -5038,8 +5106,10 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="n">
-        <v>5</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N58" t="n">
         <v>2</v>
@@ -5117,8 +5187,10 @@
       <c r="L59" t="n">
         <v>4</v>
       </c>
-      <c r="M59" t="n">
-        <v>5</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N59" t="n">
         <v>2</v>
@@ -5196,8 +5268,10 @@
       <c r="L60" t="n">
         <v>4</v>
       </c>
-      <c r="M60" t="n">
-        <v>2</v>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N60" t="n">
         <v>1</v>
@@ -5356,8 +5430,10 @@
       <c r="L62" t="n">
         <v>4</v>
       </c>
-      <c r="M62" t="n">
-        <v>4</v>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N62" t="n">
         <v>2</v>
@@ -5435,8 +5511,10 @@
       <c r="L63" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="n">
-        <v>4</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -5514,8 +5592,10 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="n">
-        <v>4</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -5755,8 +5835,10 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="n">
-        <v>5</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5834,8 +5916,10 @@
       <c r="L68" t="n">
         <v>5</v>
       </c>
-      <c r="M68" t="n">
-        <v>5</v>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N68" t="n">
         <v>2</v>
@@ -5913,8 +5997,10 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="n">
-        <v>4</v>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -5992,8 +6078,10 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="n">
-        <v>5</v>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -6071,8 +6159,10 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="n">
-        <v>5</v>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -6231,8 +6321,10 @@
       <c r="L73" t="n">
         <v>4</v>
       </c>
-      <c r="M73" t="n">
-        <v>4</v>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N73" t="n">
         <v>1</v>
@@ -6391,8 +6483,10 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="n">
-        <v>4</v>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N75" t="n">
         <v>2</v>
@@ -6470,8 +6564,10 @@
       <c r="L76" t="n">
         <v>3</v>
       </c>
-      <c r="M76" t="n">
-        <v>4</v>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N76" t="n">
         <v>2</v>
@@ -6549,8 +6645,10 @@
       <c r="L77" t="n">
         <v>4</v>
       </c>
-      <c r="M77" t="n">
-        <v>4</v>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N77" t="n">
         <v>2</v>
@@ -6628,8 +6726,10 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="n">
-        <v>4</v>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -6707,8 +6807,10 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="n">
-        <v>5</v>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -6786,8 +6888,10 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="n">
-        <v>1</v>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -6865,8 +6969,10 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="n">
-        <v>5</v>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -6944,8 +7050,10 @@
       <c r="L82" t="n">
         <v>4</v>
       </c>
-      <c r="M82" t="n">
-        <v>4</v>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -7023,8 +7131,10 @@
       <c r="L83" t="n">
         <v>3</v>
       </c>
-      <c r="M83" t="n">
-        <v>1</v>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N83" t="n">
         <v>2</v>
@@ -7183,8 +7293,10 @@
       <c r="L85" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="n">
-        <v>4</v>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N85" t="n">
         <v>2</v>
@@ -7262,8 +7374,10 @@
       <c r="L86" t="n">
         <v>4</v>
       </c>
-      <c r="M86" t="n">
-        <v>4</v>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -7341,8 +7455,10 @@
       <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="M87" t="n">
-        <v>4</v>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N87" t="n">
         <v>2</v>
@@ -7420,8 +7536,10 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="n">
-        <v>1</v>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -7499,8 +7617,10 @@
       <c r="L89" t="n">
         <v>4</v>
       </c>
-      <c r="M89" t="n">
-        <v>5</v>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N89" t="n">
         <v>2</v>
@@ -7659,8 +7779,10 @@
       <c r="L91" t="n">
         <v>5</v>
       </c>
-      <c r="M91" t="n">
-        <v>5</v>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -7738,8 +7860,10 @@
       <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="n">
-        <v>4</v>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N92" t="n">
         <v>2</v>
@@ -7817,8 +7941,10 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
-      <c r="M93" t="n">
-        <v>4</v>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N93" t="n">
         <v>2</v>
@@ -7896,8 +8022,10 @@
       <c r="L94" t="n">
         <v>2</v>
       </c>
-      <c r="M94" t="n">
-        <v>3</v>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -7975,8 +8103,10 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="n">
-        <v>5</v>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -8135,8 +8265,10 @@
       <c r="L97" t="n">
         <v>3</v>
       </c>
-      <c r="M97" t="n">
-        <v>4</v>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N97" t="n">
         <v>2</v>
@@ -8214,8 +8346,10 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="n">
-        <v>4</v>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -8293,8 +8427,10 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="n">
-        <v>1</v>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -8372,8 +8508,10 @@
       <c r="L100" t="n">
         <v>5</v>
       </c>
-      <c r="M100" t="n">
-        <v>4</v>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -8451,8 +8589,10 @@
       <c r="L101" t="n">
         <v>3</v>
       </c>
-      <c r="M101" t="n">
-        <v>1</v>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -8530,8 +8670,10 @@
       <c r="L102" t="n">
         <v>5</v>
       </c>
-      <c r="M102" t="n">
-        <v>4</v>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N102" t="n">
         <v>2</v>
@@ -8771,8 +8913,10 @@
       <c r="L105" t="n">
         <v>5</v>
       </c>
-      <c r="M105" t="n">
-        <v>5</v>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -8850,8 +8994,10 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -8929,8 +9075,10 @@
       <c r="L107" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="n">
-        <v>4</v>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -9008,8 +9156,10 @@
       <c r="L108" t="n">
         <v>2</v>
       </c>
-      <c r="M108" t="n">
-        <v>4</v>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -9087,8 +9237,10 @@
       <c r="L109" t="n">
         <v>4</v>
       </c>
-      <c r="M109" t="n">
-        <v>4</v>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -9166,8 +9318,10 @@
       <c r="L110" t="n">
         <v>4</v>
       </c>
-      <c r="M110" t="n">
-        <v>5</v>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N110" t="n">
         <v>1</v>
@@ -9245,8 +9399,10 @@
       <c r="L111" t="n">
         <v>3</v>
       </c>
-      <c r="M111" t="n">
-        <v>4</v>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -9324,8 +9480,10 @@
       <c r="L112" t="n">
         <v>1</v>
       </c>
-      <c r="M112" t="n">
-        <v>4</v>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N112" t="n">
         <v>3</v>
@@ -9403,8 +9561,10 @@
       <c r="L113" t="n">
         <v>5</v>
       </c>
-      <c r="M113" t="n">
-        <v>1</v>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -9563,8 +9723,10 @@
       <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="n">
-        <v>4</v>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -9723,8 +9885,10 @@
       <c r="L117" t="n">
         <v>4</v>
       </c>
-      <c r="M117" t="n">
-        <v>5</v>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N117" t="n">
         <v>2</v>
@@ -9964,8 +10128,10 @@
       <c r="L120" t="n">
         <v>4</v>
       </c>
-      <c r="M120" t="n">
-        <v>4</v>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N120" t="n">
         <v>2</v>
@@ -10043,8 +10209,10 @@
       <c r="L121" t="n">
         <v>4</v>
       </c>
-      <c r="M121" t="n">
-        <v>4</v>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -10122,8 +10290,10 @@
       <c r="L122" t="n">
         <v>2</v>
       </c>
-      <c r="M122" t="n">
-        <v>4</v>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N122" t="n">
         <v>2</v>
@@ -10201,8 +10371,10 @@
       <c r="L123" t="n">
         <v>4</v>
       </c>
-      <c r="M123" t="n">
-        <v>4</v>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -10361,8 +10533,10 @@
       <c r="L125" t="n">
         <v>5</v>
       </c>
-      <c r="M125" t="n">
-        <v>1</v>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N125" t="n">
         <v>3</v>
@@ -10440,8 +10614,10 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="n">
-        <v>4</v>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -10681,8 +10857,10 @@
       <c r="L129" t="n">
         <v>4</v>
       </c>
-      <c r="M129" t="n">
-        <v>4</v>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -10760,8 +10938,10 @@
       <c r="L130" t="n">
         <v>2</v>
       </c>
-      <c r="M130" t="n">
-        <v>5</v>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -10839,8 +11019,10 @@
       <c r="L131" t="n">
         <v>4</v>
       </c>
-      <c r="M131" t="n">
-        <v>4</v>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N131" t="n">
         <v>2</v>
@@ -10918,8 +11100,10 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="n">
-        <v>4</v>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -11159,8 +11343,10 @@
       <c r="L135" t="n">
         <v>4</v>
       </c>
-      <c r="M135" t="n">
-        <v>4</v>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N135" t="n">
         <v>2</v>
@@ -11238,8 +11424,10 @@
       <c r="L136" t="n">
         <v>4</v>
       </c>
-      <c r="M136" t="n">
-        <v>5</v>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -11317,8 +11505,10 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="n">
-        <v>1</v>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N137" t="n">
         <v>1</v>
@@ -11477,8 +11667,10 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="n">
-        <v>4</v>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -11556,8 +11748,10 @@
       <c r="L140" t="n">
         <v>3</v>
       </c>
-      <c r="M140" t="n">
-        <v>5</v>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N140" t="n">
         <v>1</v>
@@ -11635,8 +11829,10 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="n">
-        <v>1</v>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N141" t="n">
         <v>2</v>
@@ -11795,8 +11991,10 @@
       <c r="L143" t="n">
         <v>5</v>
       </c>
-      <c r="M143" t="n">
-        <v>1</v>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N143" t="n">
         <v>2</v>
@@ -11874,8 +12072,10 @@
       <c r="L144" t="n">
         <v>4</v>
       </c>
-      <c r="M144" t="n">
-        <v>5</v>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N144" t="n">
         <v>2</v>
@@ -11953,8 +12153,10 @@
       <c r="L145" t="n">
         <v>3</v>
       </c>
-      <c r="M145" t="n">
-        <v>5</v>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N145" t="n">
         <v>2</v>
@@ -12113,8 +12315,10 @@
       <c r="L147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="n">
-        <v>5</v>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N147" t="n">
         <v>2</v>
@@ -12192,8 +12396,10 @@
       <c r="L148" t="n">
         <v>2</v>
       </c>
-      <c r="M148" t="n">
-        <v>4</v>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -12271,8 +12477,10 @@
       <c r="L149" t="n">
         <v>4</v>
       </c>
-      <c r="M149" t="n">
-        <v>4</v>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N149" t="n">
         <v>2</v>
@@ -12350,8 +12558,10 @@
       <c r="L150" t="n">
         <v>4</v>
       </c>
-      <c r="M150" t="n">
-        <v>4</v>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N150" t="n">
         <v>1</v>
@@ -12429,8 +12639,10 @@
       <c r="L151" t="n">
         <v>4</v>
       </c>
-      <c r="M151" t="n">
-        <v>4</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N151" t="n">
         <v>2</v>
@@ -12508,8 +12720,10 @@
       <c r="L152" t="n">
         <v>5</v>
       </c>
-      <c r="M152" t="n">
-        <v>4</v>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N152" t="n">
         <v>1</v>
@@ -12587,8 +12801,10 @@
       <c r="L153" t="n">
         <v>3</v>
       </c>
-      <c r="M153" t="n">
-        <v>4</v>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N153" t="n">
         <v>1</v>
@@ -12666,8 +12882,10 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="n">
-        <v>4</v>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N154" t="n">
         <v>1</v>
@@ -12745,8 +12963,10 @@
       <c r="L155" t="n">
         <v>2</v>
       </c>
-      <c r="M155" t="n">
-        <v>5</v>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -12905,8 +13125,10 @@
       <c r="L157" t="n">
         <v>2</v>
       </c>
-      <c r="M157" t="n">
-        <v>4</v>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -13146,8 +13368,10 @@
       <c r="L160" t="n">
         <v>2</v>
       </c>
-      <c r="M160" t="n">
-        <v>5</v>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N160" t="n">
         <v>2</v>
@@ -13225,8 +13449,10 @@
       <c r="L161" t="n">
         <v>4</v>
       </c>
-      <c r="M161" t="n">
-        <v>4</v>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N161" t="n">
         <v>2</v>
@@ -13385,8 +13611,10 @@
       <c r="L163" t="n">
         <v>3</v>
       </c>
-      <c r="M163" t="n">
-        <v>4</v>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -13464,8 +13692,10 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="n">
-        <v>4</v>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -13543,8 +13773,10 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="n">
-        <v>3</v>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -13622,8 +13854,10 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="n">
-        <v>1</v>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -13701,8 +13935,10 @@
       <c r="L167" t="n">
         <v>4</v>
       </c>
-      <c r="M167" t="n">
-        <v>4</v>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N167" t="n">
         <v>2</v>
@@ -13780,8 +14016,10 @@
       <c r="L168" t="n">
         <v>4</v>
       </c>
-      <c r="M168" t="n">
-        <v>3</v>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N168" t="n">
         <v>1</v>
@@ -14021,8 +14259,10 @@
       <c r="L171" t="n">
         <v>2</v>
       </c>
-      <c r="M171" t="n">
-        <v>5</v>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -14100,8 +14340,10 @@
       <c r="L172" t="n">
         <v>5</v>
       </c>
-      <c r="M172" t="n">
-        <v>4</v>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N172" t="n">
         <v>1</v>
@@ -14179,8 +14421,10 @@
       <c r="L173" t="n">
         <v>4</v>
       </c>
-      <c r="M173" t="n">
-        <v>3</v>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N173" t="n">
         <v>2</v>
@@ -14258,8 +14502,10 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="n">
-        <v>4</v>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -14337,8 +14583,10 @@
       <c r="L175" t="n">
         <v>4</v>
       </c>
-      <c r="M175" t="n">
-        <v>4</v>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N175" t="n">
         <v>2</v>
@@ -14416,8 +14664,10 @@
       <c r="L176" t="n">
         <v>5</v>
       </c>
-      <c r="M176" t="n">
-        <v>4</v>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N176" t="n">
         <v>2</v>
@@ -14495,8 +14745,10 @@
       <c r="L177" t="n">
         <v>5</v>
       </c>
-      <c r="M177" t="n">
-        <v>5</v>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N177" t="n">
         <v>1</v>
@@ -14574,8 +14826,10 @@
       <c r="L178" t="n">
         <v>5</v>
       </c>
-      <c r="M178" t="n">
-        <v>5</v>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N178" t="n">
         <v>1</v>
@@ -14653,8 +14907,10 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="n">
-        <v>1</v>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N179" t="n">
         <v>1</v>
@@ -14813,8 +15069,10 @@
       <c r="L181" t="n">
         <v>5</v>
       </c>
-      <c r="M181" t="n">
-        <v>5</v>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -14973,8 +15231,10 @@
       <c r="L183" t="n">
         <v>5</v>
       </c>
-      <c r="M183" t="n">
-        <v>5</v>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -15052,8 +15312,10 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="n">
-        <v>5</v>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N184" t="n">
         <v>2</v>
@@ -15131,8 +15393,10 @@
       <c r="L185" t="n">
         <v>4</v>
       </c>
-      <c r="M185" t="n">
-        <v>5</v>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N185" t="n">
         <v>2</v>
@@ -15210,8 +15474,10 @@
       <c r="L186" t="n">
         <v>4</v>
       </c>
-      <c r="M186" t="n">
-        <v>5</v>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N186" t="n">
         <v>2</v>
@@ -15370,8 +15636,10 @@
       <c r="L188" t="n">
         <v>3</v>
       </c>
-      <c r="M188" t="n">
-        <v>4</v>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -15449,8 +15717,10 @@
       <c r="L189" t="n">
         <v>4</v>
       </c>
-      <c r="M189" t="n">
-        <v>5</v>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N189" t="n">
         <v>2</v>
@@ -15771,8 +16041,10 @@
       <c r="L193" t="n">
         <v>5</v>
       </c>
-      <c r="M193" t="n">
-        <v>3</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N193" t="n">
         <v>1</v>
@@ -15850,8 +16122,10 @@
       <c r="L194" t="n">
         <v>4</v>
       </c>
-      <c r="M194" t="n">
-        <v>4</v>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N194" t="n">
         <v>2</v>
@@ -15929,8 +16203,10 @@
       <c r="L195" t="n">
         <v>5</v>
       </c>
-      <c r="M195" t="n">
-        <v>4</v>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N195" t="n">
         <v>1</v>
@@ -16008,8 +16284,10 @@
       <c r="L196" t="n">
         <v>4</v>
       </c>
-      <c r="M196" t="n">
-        <v>4</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N196" t="n">
         <v>3</v>
@@ -16087,8 +16365,10 @@
       <c r="L197" t="n">
         <v>4</v>
       </c>
-      <c r="M197" t="n">
-        <v>4</v>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N197" t="n">
         <v>2</v>
@@ -16247,8 +16527,10 @@
       <c r="L199" t="n">
         <v>2</v>
       </c>
-      <c r="M199" t="n">
-        <v>4</v>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N199" t="n">
         <v>2</v>
@@ -16326,8 +16608,10 @@
       <c r="L200" t="n">
         <v>3</v>
       </c>
-      <c r="M200" t="n">
-        <v>5</v>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -16405,8 +16689,10 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
-      <c r="M201" t="n">
-        <v>4</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -16565,8 +16851,10 @@
       <c r="L203" t="n">
         <v>3</v>
       </c>
-      <c r="M203" t="n">
-        <v>1</v>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -16725,8 +17013,10 @@
       <c r="L205" t="n">
         <v>4</v>
       </c>
-      <c r="M205" t="n">
-        <v>4</v>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -17047,8 +17337,10 @@
       <c r="L209" t="n">
         <v>3</v>
       </c>
-      <c r="M209" t="n">
-        <v>5</v>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N209" t="n">
         <v>2</v>
@@ -17126,8 +17418,10 @@
       <c r="L210" t="n">
         <v>2</v>
       </c>
-      <c r="M210" t="n">
-        <v>5</v>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N210" t="n">
         <v>2</v>
@@ -17205,8 +17499,10 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="n">
-        <v>4</v>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -17365,8 +17661,10 @@
       <c r="L213" t="n">
         <v>2</v>
       </c>
-      <c r="M213" t="n">
-        <v>4</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N213" t="n">
         <v>3</v>
@@ -17444,8 +17742,10 @@
       <c r="L214" t="n">
         <v>5</v>
       </c>
-      <c r="M214" t="n">
-        <v>4</v>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -17523,8 +17823,10 @@
       <c r="L215" t="n">
         <v>5</v>
       </c>
-      <c r="M215" t="n">
-        <v>5</v>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N215" t="n">
         <v>2</v>
@@ -17764,8 +18066,10 @@
       <c r="L218" t="n">
         <v>5</v>
       </c>
-      <c r="M218" t="n">
-        <v>4</v>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N218" t="n">
         <v>2</v>
@@ -17924,8 +18228,10 @@
       <c r="L220" t="n">
         <v>4</v>
       </c>
-      <c r="M220" t="n">
-        <v>1</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -18165,8 +18471,10 @@
       <c r="L223" t="n">
         <v>5</v>
       </c>
-      <c r="M223" t="n">
-        <v>1</v>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N223" t="n">
         <v>2</v>
@@ -18244,8 +18552,10 @@
       <c r="L224" t="n">
         <v>5</v>
       </c>
-      <c r="M224" t="n">
-        <v>4</v>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -18323,8 +18633,10 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="n">
-        <v>5</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -18402,8 +18714,10 @@
       <c r="L226" t="n">
         <v>5</v>
       </c>
-      <c r="M226" t="n">
-        <v>1</v>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N226" t="n">
         <v>1</v>
@@ -18481,8 +18795,10 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="n">
-        <v>4</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -18641,8 +18957,10 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="n">
-        <v>4</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N229" t="n">
         <v>3</v>
@@ -18720,8 +19038,10 @@
       <c r="L230" t="n">
         <v>5</v>
       </c>
-      <c r="M230" t="n">
-        <v>5</v>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N230" t="n">
         <v>2</v>
@@ -18961,8 +19281,10 @@
       <c r="L233" t="n">
         <v>5</v>
       </c>
-      <c r="M233" t="n">
-        <v>4</v>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -19040,8 +19362,10 @@
       <c r="L234" t="n">
         <v>2</v>
       </c>
-      <c r="M234" t="n">
-        <v>4</v>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N234" t="n">
         <v>2</v>
@@ -19200,8 +19524,10 @@
       <c r="L236" t="n">
         <v>4</v>
       </c>
-      <c r="M236" t="n">
-        <v>4</v>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N236" t="n">
         <v>2</v>
@@ -19279,8 +19605,10 @@
       <c r="L237" t="n">
         <v>5</v>
       </c>
-      <c r="M237" t="n">
-        <v>5</v>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N237" t="n">
         <v>2</v>
@@ -19358,8 +19686,10 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="n">
-        <v>4</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -19437,8 +19767,10 @@
       <c r="L239" t="n">
         <v>3</v>
       </c>
-      <c r="M239" t="n">
-        <v>4</v>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N239" t="n">
         <v>3</v>
@@ -19516,8 +19848,10 @@
       <c r="L240" t="n">
         <v>5</v>
       </c>
-      <c r="M240" t="n">
-        <v>4</v>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N240" t="n">
         <v>2</v>
@@ -19595,8 +19929,10 @@
       <c r="L241" t="n">
         <v>3</v>
       </c>
-      <c r="M241" t="n">
-        <v>4</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -19674,8 +20010,10 @@
       <c r="L242" t="n">
         <v>2</v>
       </c>
-      <c r="M242" t="n">
-        <v>5</v>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N242" t="n">
         <v>2</v>
@@ -19834,8 +20172,10 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="n">
-        <v>4</v>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N244" t="n">
         <v>2</v>
@@ -19913,8 +20253,10 @@
       <c r="L245" t="n">
         <v>5</v>
       </c>
-      <c r="M245" t="n">
-        <v>4</v>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N245" t="n">
         <v>2</v>
@@ -19992,8 +20334,10 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="n">
-        <v>4</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -20071,8 +20415,10 @@
       <c r="L247" t="n">
         <v>2</v>
       </c>
-      <c r="M247" t="n">
-        <v>4</v>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N247" t="n">
         <v>3</v>
@@ -20312,8 +20658,10 @@
       <c r="L250" t="n">
         <v>5</v>
       </c>
-      <c r="M250" t="n">
-        <v>1</v>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N250" t="n">
         <v>2</v>
@@ -20391,8 +20739,10 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="n">
-        <v>1</v>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N251" t="n">
         <v>1</v>
@@ -20470,8 +20820,10 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="n">
-        <v>4</v>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -20711,8 +21063,10 @@
       <c r="L255" t="n">
         <v>4</v>
       </c>
-      <c r="M255" t="n">
-        <v>1</v>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N255" t="n">
         <v>2</v>
@@ -20790,8 +21144,10 @@
       <c r="L256" t="n">
         <v>4</v>
       </c>
-      <c r="M256" t="n">
-        <v>3</v>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N256" t="n">
         <v>2</v>
@@ -20869,8 +21225,10 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="n">
-        <v>4</v>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N257" t="n">
         <v>2</v>
@@ -20948,8 +21306,10 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="n">
-        <v>1</v>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N258" t="n">
         <v>1</v>
@@ -21027,8 +21387,10 @@
       <c r="L259" t="n">
         <v>2</v>
       </c>
-      <c r="M259" t="n">
-        <v>4</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N259" t="n">
         <v>2</v>
@@ -21106,8 +21468,10 @@
       <c r="L260" t="n">
         <v>5</v>
       </c>
-      <c r="M260" t="n">
-        <v>1</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -21266,8 +21630,10 @@
       <c r="L262" t="n">
         <v>2</v>
       </c>
-      <c r="M262" t="n">
-        <v>2</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -21345,8 +21711,10 @@
       <c r="L263" t="n">
         <v>1</v>
       </c>
-      <c r="M263" t="n">
-        <v>4</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N263" t="n">
         <v>3</v>
@@ -21424,8 +21792,10 @@
       <c r="L264" t="n">
         <v>3</v>
       </c>
-      <c r="M264" t="n">
-        <v>1</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -21584,8 +21954,10 @@
       <c r="L266" t="n">
         <v>4</v>
       </c>
-      <c r="M266" t="n">
-        <v>4</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -21663,8 +22035,10 @@
       <c r="L267" t="n">
         <v>4</v>
       </c>
-      <c r="M267" t="n">
-        <v>4</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -21742,8 +22116,10 @@
       <c r="L268" t="n">
         <v>5</v>
       </c>
-      <c r="M268" t="n">
-        <v>3</v>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N268" t="n">
         <v>1</v>
@@ -21821,8 +22197,10 @@
       <c r="L269" t="n">
         <v>5</v>
       </c>
-      <c r="M269" t="n">
-        <v>4</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -21900,8 +22278,10 @@
       <c r="L270" t="n">
         <v>4</v>
       </c>
-      <c r="M270" t="n">
-        <v>4</v>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N270" t="n">
         <v>2</v>
@@ -22060,8 +22440,10 @@
       <c r="L272" t="n">
         <v>4</v>
       </c>
-      <c r="M272" t="n">
-        <v>4</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -22220,8 +22602,10 @@
       <c r="L274" t="n">
         <v>2</v>
       </c>
-      <c r="M274" t="n">
-        <v>4</v>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N274" t="n">
         <v>2</v>
@@ -22299,8 +22683,10 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="n">
-        <v>4</v>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -22378,8 +22764,10 @@
       <c r="L276" t="n">
         <v>5</v>
       </c>
-      <c r="M276" t="n">
-        <v>5</v>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -22457,8 +22845,10 @@
       <c r="L277" t="n">
         <v>2</v>
       </c>
-      <c r="M277" t="n">
-        <v>5</v>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -22617,8 +23007,10 @@
       <c r="L279" t="n">
         <v>1</v>
       </c>
-      <c r="M279" t="n">
-        <v>1</v>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N279" t="n">
         <v>0</v>
@@ -22777,8 +23169,10 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="n">
-        <v>5</v>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -22856,8 +23250,10 @@
       <c r="L282" t="n">
         <v>4</v>
       </c>
-      <c r="M282" t="n">
-        <v>1</v>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -22935,8 +23331,10 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="n">
-        <v>1</v>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -23014,8 +23412,10 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="n">
-        <v>4</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N284" t="n">
         <v>2</v>
@@ -23093,8 +23493,10 @@
       <c r="L285" t="n">
         <v>4</v>
       </c>
-      <c r="M285" t="n">
-        <v>4</v>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -23172,8 +23574,10 @@
       <c r="L286" t="n">
         <v>5</v>
       </c>
-      <c r="M286" t="n">
-        <v>5</v>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -23251,8 +23655,10 @@
       <c r="L287" t="n">
         <v>3</v>
       </c>
-      <c r="M287" t="n">
-        <v>4</v>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -23492,8 +23898,10 @@
       <c r="L290" t="n">
         <v>4</v>
       </c>
-      <c r="M290" t="n">
-        <v>5</v>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N290" t="n">
         <v>2</v>
@@ -23571,8 +23979,10 @@
       <c r="L291" t="n">
         <v>2</v>
       </c>
-      <c r="M291" t="n">
-        <v>5</v>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="N291" t="n">
         <v>1</v>
@@ -23731,8 +24141,10 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="n">
-        <v>4</v>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N293" t="n">
         <v>2</v>
@@ -23810,8 +24222,10 @@
       <c r="L294" t="n">
         <v>4</v>
       </c>
-      <c r="M294" t="n">
-        <v>4</v>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="N294" t="n">
         <v>2</v>

--- a/data/split/val.xlsx
+++ b/data/split/val.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W294"/>
+  <dimension ref="A1:X294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,11 @@
           <t>pass_loc_sin</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>men</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -570,10 +575,8 @@
       <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M2" t="n">
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -612,6 +615,9 @@
       </c>
       <c r="W2" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -694,6 +700,9 @@
       <c r="W3" t="n">
         <v>-1</v>
       </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -732,10 +741,8 @@
       <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M4" t="n">
+        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -774,6 +781,9 @@
       </c>
       <c r="W4" t="n">
         <v>-1</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -856,6 +866,9 @@
       <c r="W5" t="n">
         <v>-1</v>
       </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -894,10 +907,8 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M6" t="n">
+        <v>4</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -936,6 +947,9 @@
       </c>
       <c r="W6" t="n">
         <v>-1</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1018,6 +1032,9 @@
       <c r="W7" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1099,6 +1116,9 @@
       <c r="W8" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1137,10 +1157,8 @@
       <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M9" t="n">
+        <v>5</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1179,6 +1197,9 @@
       </c>
       <c r="W9" t="n">
         <v>-1</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1218,10 +1239,8 @@
       <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M10" t="n">
+        <v>5</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1260,6 +1279,9 @@
       </c>
       <c r="W10" t="n">
         <v>-1</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1299,10 +1321,8 @@
       <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M11" t="n">
+        <v>5</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1341,6 +1361,9 @@
       </c>
       <c r="W11" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1380,10 +1403,8 @@
       <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M12" t="n">
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1422,6 +1443,9 @@
       </c>
       <c r="W12" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1504,6 +1528,9 @@
       <c r="W13" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1585,6 +1612,9 @@
       <c r="W14" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1623,10 +1653,8 @@
       <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M15" t="n">
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
@@ -1665,6 +1693,9 @@
       </c>
       <c r="W15" t="n">
         <v>-1</v>
+      </c>
+      <c r="X15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1704,10 +1735,8 @@
       <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M16" t="n">
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
@@ -1746,6 +1775,9 @@
       </c>
       <c r="W16" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1785,10 +1817,8 @@
       <c r="L17" t="n">
         <v>4</v>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M17" t="n">
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1827,6 +1857,9 @@
       </c>
       <c r="W17" t="n">
         <v>-1</v>
+      </c>
+      <c r="X17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1866,10 +1899,8 @@
       <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M18" t="n">
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1908,6 +1939,9 @@
       </c>
       <c r="W18" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1947,10 +1981,8 @@
       <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M19" t="n">
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -1989,6 +2021,9 @@
       </c>
       <c r="W19" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2028,10 +2063,8 @@
       <c r="L20" t="n">
         <v>5</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M20" t="n">
+        <v>4</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -2070,6 +2103,9 @@
       </c>
       <c r="W20" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2109,10 +2145,8 @@
       <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M21" t="n">
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -2151,6 +2185,9 @@
       </c>
       <c r="W21" t="n">
         <v>-1</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2190,10 +2227,8 @@
       <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M22" t="n">
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2232,6 +2267,9 @@
       </c>
       <c r="W22" t="n">
         <v>-1</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2314,6 +2352,9 @@
       <c r="W23" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2352,10 +2393,8 @@
       <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M24" t="n">
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2394,6 +2433,9 @@
       </c>
       <c r="W24" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2476,6 +2518,9 @@
       <c r="W25" t="n">
         <v>-1</v>
       </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2514,10 +2559,8 @@
       <c r="L26" t="n">
         <v>4</v>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M26" t="n">
+        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -2556,6 +2599,9 @@
       </c>
       <c r="W26" t="n">
         <v>1</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2595,10 +2641,8 @@
       <c r="L27" t="n">
         <v>4</v>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M27" t="n">
+        <v>4</v>
       </c>
       <c r="N27" t="n">
         <v>2</v>
@@ -2636,6 +2680,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2719,6 +2766,9 @@
       <c r="W28" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2757,10 +2807,8 @@
       <c r="L29" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M29" t="n">
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
@@ -2799,6 +2847,9 @@
       </c>
       <c r="W29" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2838,10 +2889,8 @@
       <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M30" t="n">
+        <v>4</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
@@ -2880,6 +2929,9 @@
       </c>
       <c r="W30" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2962,6 +3014,9 @@
       <c r="W31" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3000,10 +3055,8 @@
       <c r="L32" t="n">
         <v>4</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M32" t="n">
+        <v>4</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
@@ -3042,6 +3095,9 @@
       </c>
       <c r="W32" t="n">
         <v>-1</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3081,10 +3137,8 @@
       <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M33" t="n">
+        <v>4</v>
       </c>
       <c r="N33" t="n">
         <v>2</v>
@@ -3123,6 +3177,9 @@
       </c>
       <c r="W33" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3162,10 +3219,8 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M34" t="n">
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -3204,6 +3259,9 @@
       </c>
       <c r="W34" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3286,6 +3344,9 @@
       <c r="W35" t="n">
         <v>-1</v>
       </c>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3324,10 +3385,8 @@
       <c r="L36" t="n">
         <v>5</v>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M36" t="n">
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>2</v>
@@ -3366,6 +3425,9 @@
       </c>
       <c r="W36" t="n">
         <v>-1</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3405,10 +3467,8 @@
       <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M37" t="n">
+        <v>5</v>
       </c>
       <c r="N37" t="n">
         <v>2</v>
@@ -3447,6 +3507,9 @@
       </c>
       <c r="W37" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3529,6 +3592,9 @@
       <c r="W38" t="n">
         <v>-1</v>
       </c>
+      <c r="X38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3610,6 +3676,9 @@
       <c r="W39" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3691,6 +3760,9 @@
       <c r="W40" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3772,6 +3844,9 @@
       <c r="W41" t="n">
         <v>-1</v>
       </c>
+      <c r="X41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3810,10 +3885,8 @@
       <c r="L42" t="n">
         <v>3</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M42" t="n">
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>2</v>
@@ -3852,6 +3925,9 @@
       </c>
       <c r="W42" t="n">
         <v>-1</v>
+      </c>
+      <c r="X42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3891,10 +3967,8 @@
       <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M43" t="n">
+        <v>3</v>
       </c>
       <c r="N43" t="n">
         <v>2</v>
@@ -3933,6 +4007,9 @@
       </c>
       <c r="W43" t="n">
         <v>1</v>
+      </c>
+      <c r="X43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4015,6 +4092,9 @@
       <c r="W44" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4053,10 +4133,8 @@
       <c r="L45" t="n">
         <v>4</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M45" t="n">
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -4095,6 +4173,9 @@
       </c>
       <c r="W45" t="n">
         <v>-1</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4134,10 +4215,8 @@
       <c r="L46" t="n">
         <v>4</v>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M46" t="n">
+        <v>3</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
@@ -4176,6 +4255,9 @@
       </c>
       <c r="W46" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4258,6 +4340,9 @@
       <c r="W47" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4339,6 +4424,9 @@
       <c r="W48" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4420,6 +4508,9 @@
       <c r="W49" t="n">
         <v>-1</v>
       </c>
+      <c r="X49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4458,10 +4549,8 @@
       <c r="L50" t="n">
         <v>5</v>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M50" t="n">
+        <v>1</v>
       </c>
       <c r="N50" t="n">
         <v>2</v>
@@ -4500,6 +4589,9 @@
       </c>
       <c r="W50" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4539,10 +4631,8 @@
       <c r="L51" t="n">
         <v>5</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M51" t="n">
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
@@ -4581,6 +4671,9 @@
       </c>
       <c r="W51" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4663,6 +4756,9 @@
       <c r="W52" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4701,10 +4797,8 @@
       <c r="L53" t="n">
         <v>4</v>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M53" t="n">
+        <v>4</v>
       </c>
       <c r="N53" t="n">
         <v>2</v>
@@ -4743,6 +4837,9 @@
       </c>
       <c r="W53" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4825,6 +4922,9 @@
       <c r="W54" t="n">
         <v>-1</v>
       </c>
+      <c r="X54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4863,10 +4963,8 @@
       <c r="L55" t="n">
         <v>4</v>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M55" t="n">
+        <v>4</v>
       </c>
       <c r="N55" t="n">
         <v>2</v>
@@ -4905,6 +5003,9 @@
       </c>
       <c r="W55" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4987,6 +5088,9 @@
       <c r="W56" t="n">
         <v>-1</v>
       </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5025,10 +5129,8 @@
       <c r="L57" t="n">
         <v>3</v>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M57" t="n">
+        <v>1</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -5067,6 +5169,9 @@
       </c>
       <c r="W57" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5106,10 +5211,8 @@
       <c r="L58" t="n">
         <v>5</v>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M58" t="n">
+        <v>5</v>
       </c>
       <c r="N58" t="n">
         <v>2</v>
@@ -5148,6 +5251,9 @@
       </c>
       <c r="W58" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5187,10 +5293,8 @@
       <c r="L59" t="n">
         <v>4</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M59" t="n">
+        <v>5</v>
       </c>
       <c r="N59" t="n">
         <v>2</v>
@@ -5229,6 +5333,9 @@
       </c>
       <c r="W59" t="n">
         <v>-1</v>
+      </c>
+      <c r="X59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5268,10 +5375,8 @@
       <c r="L60" t="n">
         <v>4</v>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M60" t="n">
+        <v>2</v>
       </c>
       <c r="N60" t="n">
         <v>1</v>
@@ -5310,6 +5415,9 @@
       </c>
       <c r="W60" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5392,6 +5500,9 @@
       <c r="W61" t="n">
         <v>-1</v>
       </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5430,10 +5541,8 @@
       <c r="L62" t="n">
         <v>4</v>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M62" t="n">
+        <v>4</v>
       </c>
       <c r="N62" t="n">
         <v>2</v>
@@ -5472,6 +5581,9 @@
       </c>
       <c r="W62" t="n">
         <v>-1</v>
+      </c>
+      <c r="X62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5511,10 +5623,8 @@
       <c r="L63" t="n">
         <v>2</v>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M63" t="n">
+        <v>4</v>
       </c>
       <c r="N63" t="n">
         <v>2</v>
@@ -5552,6 +5662,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5592,10 +5705,8 @@
       <c r="L64" t="n">
         <v>2</v>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M64" t="n">
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>2</v>
@@ -5634,6 +5745,9 @@
       </c>
       <c r="W64" t="n">
         <v>1</v>
+      </c>
+      <c r="X64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5716,6 +5830,9 @@
       <c r="W65" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5797,6 +5914,9 @@
       <c r="W66" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5835,10 +5955,8 @@
       <c r="L67" t="n">
         <v>4</v>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M67" t="n">
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>2</v>
@@ -5877,6 +5995,9 @@
       </c>
       <c r="W67" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5916,10 +6037,8 @@
       <c r="L68" t="n">
         <v>5</v>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M68" t="n">
+        <v>5</v>
       </c>
       <c r="N68" t="n">
         <v>2</v>
@@ -5958,6 +6077,9 @@
       </c>
       <c r="W68" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5997,10 +6119,8 @@
       <c r="L69" t="n">
         <v>2</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M69" t="n">
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -6039,6 +6159,9 @@
       </c>
       <c r="W69" t="n">
         <v>-1</v>
+      </c>
+      <c r="X69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6078,10 +6201,8 @@
       <c r="L70" t="n">
         <v>4</v>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M70" t="n">
+        <v>5</v>
       </c>
       <c r="N70" t="n">
         <v>2</v>
@@ -6120,6 +6241,9 @@
       </c>
       <c r="W70" t="n">
         <v>-1</v>
+      </c>
+      <c r="X70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6159,10 +6283,8 @@
       <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M71" t="n">
+        <v>5</v>
       </c>
       <c r="N71" t="n">
         <v>2</v>
@@ -6201,6 +6323,9 @@
       </c>
       <c r="W71" t="n">
         <v>-1</v>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6283,6 +6408,9 @@
       <c r="W72" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6321,10 +6449,8 @@
       <c r="L73" t="n">
         <v>4</v>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M73" t="n">
+        <v>4</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
@@ -6363,6 +6489,9 @@
       </c>
       <c r="W73" t="n">
         <v>-1</v>
+      </c>
+      <c r="X73" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6445,6 +6574,9 @@
       <c r="W74" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X74" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6483,10 +6615,8 @@
       <c r="L75" t="n">
         <v>4</v>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M75" t="n">
+        <v>4</v>
       </c>
       <c r="N75" t="n">
         <v>2</v>
@@ -6525,6 +6655,9 @@
       </c>
       <c r="W75" t="n">
         <v>-1</v>
+      </c>
+      <c r="X75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6564,10 +6697,8 @@
       <c r="L76" t="n">
         <v>3</v>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M76" t="n">
+        <v>4</v>
       </c>
       <c r="N76" t="n">
         <v>2</v>
@@ -6606,6 +6737,9 @@
       </c>
       <c r="W76" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -6645,10 +6779,8 @@
       <c r="L77" t="n">
         <v>4</v>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M77" t="n">
+        <v>4</v>
       </c>
       <c r="N77" t="n">
         <v>2</v>
@@ -6687,6 +6819,9 @@
       </c>
       <c r="W77" t="n">
         <v>-1</v>
+      </c>
+      <c r="X77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -6726,10 +6861,8 @@
       <c r="L78" t="n">
         <v>2</v>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M78" t="n">
+        <v>4</v>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -6768,6 +6901,9 @@
       </c>
       <c r="W78" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6807,10 +6943,8 @@
       <c r="L79" t="n">
         <v>4</v>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M79" t="n">
+        <v>5</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
@@ -6849,6 +6983,9 @@
       </c>
       <c r="W79" t="n">
         <v>-1</v>
+      </c>
+      <c r="X79" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -6888,10 +7025,8 @@
       <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M80" t="n">
+        <v>1</v>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -6930,6 +7065,9 @@
       </c>
       <c r="W80" t="n">
         <v>-1</v>
+      </c>
+      <c r="X80" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -6969,10 +7107,8 @@
       <c r="L81" t="n">
         <v>2</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M81" t="n">
+        <v>5</v>
       </c>
       <c r="N81" t="n">
         <v>2</v>
@@ -7011,6 +7147,9 @@
       </c>
       <c r="W81" t="n">
         <v>-1</v>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -7050,10 +7189,8 @@
       <c r="L82" t="n">
         <v>4</v>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M82" t="n">
+        <v>4</v>
       </c>
       <c r="N82" t="n">
         <v>2</v>
@@ -7092,6 +7229,9 @@
       </c>
       <c r="W82" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X82" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -7131,10 +7271,8 @@
       <c r="L83" t="n">
         <v>3</v>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M83" t="n">
+        <v>1</v>
       </c>
       <c r="N83" t="n">
         <v>2</v>
@@ -7173,6 +7311,9 @@
       </c>
       <c r="W83" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X83" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -7255,6 +7396,9 @@
       <c r="W84" t="n">
         <v>-1</v>
       </c>
+      <c r="X84" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7293,10 +7437,8 @@
       <c r="L85" t="n">
         <v>3</v>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M85" t="n">
+        <v>4</v>
       </c>
       <c r="N85" t="n">
         <v>2</v>
@@ -7335,6 +7477,9 @@
       </c>
       <c r="W85" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X85" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -7374,10 +7519,8 @@
       <c r="L86" t="n">
         <v>4</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M86" t="n">
+        <v>4</v>
       </c>
       <c r="N86" t="n">
         <v>2</v>
@@ -7416,6 +7559,9 @@
       </c>
       <c r="W86" t="n">
         <v>-1</v>
+      </c>
+      <c r="X86" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -7455,10 +7601,8 @@
       <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M87" t="n">
+        <v>4</v>
       </c>
       <c r="N87" t="n">
         <v>2</v>
@@ -7497,6 +7641,9 @@
       </c>
       <c r="W87" t="n">
         <v>-1</v>
+      </c>
+      <c r="X87" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7536,10 +7683,8 @@
       <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M88" t="n">
+        <v>1</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -7578,6 +7723,9 @@
       </c>
       <c r="W88" t="n">
         <v>-1</v>
+      </c>
+      <c r="X88" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -7617,10 +7765,8 @@
       <c r="L89" t="n">
         <v>4</v>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M89" t="n">
+        <v>5</v>
       </c>
       <c r="N89" t="n">
         <v>2</v>
@@ -7659,6 +7805,9 @@
       </c>
       <c r="W89" t="n">
         <v>-1</v>
+      </c>
+      <c r="X89" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7741,6 +7890,9 @@
       <c r="W90" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7779,10 +7931,8 @@
       <c r="L91" t="n">
         <v>5</v>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M91" t="n">
+        <v>5</v>
       </c>
       <c r="N91" t="n">
         <v>2</v>
@@ -7821,6 +7971,9 @@
       </c>
       <c r="W91" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X91" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7860,10 +8013,8 @@
       <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M92" t="n">
+        <v>4</v>
       </c>
       <c r="N92" t="n">
         <v>2</v>
@@ -7902,6 +8053,9 @@
       </c>
       <c r="W92" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X92" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7941,10 +8095,8 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M93" t="n">
+        <v>4</v>
       </c>
       <c r="N93" t="n">
         <v>2</v>
@@ -7983,6 +8135,9 @@
       </c>
       <c r="W93" t="n">
         <v>1</v>
+      </c>
+      <c r="X93" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8022,10 +8177,8 @@
       <c r="L94" t="n">
         <v>2</v>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M94" t="n">
+        <v>3</v>
       </c>
       <c r="N94" t="n">
         <v>2</v>
@@ -8064,6 +8217,9 @@
       </c>
       <c r="W94" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -8103,10 +8259,8 @@
       <c r="L95" t="n">
         <v>4</v>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M95" t="n">
+        <v>5</v>
       </c>
       <c r="N95" t="n">
         <v>2</v>
@@ -8145,6 +8299,9 @@
       </c>
       <c r="W95" t="n">
         <v>-1</v>
+      </c>
+      <c r="X95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -8227,6 +8384,9 @@
       <c r="W96" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -8265,10 +8425,8 @@
       <c r="L97" t="n">
         <v>3</v>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M97" t="n">
+        <v>4</v>
       </c>
       <c r="N97" t="n">
         <v>2</v>
@@ -8307,6 +8465,9 @@
       </c>
       <c r="W97" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X97" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -8346,10 +8507,8 @@
       <c r="L98" t="n">
         <v>4</v>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M98" t="n">
+        <v>4</v>
       </c>
       <c r="N98" t="n">
         <v>2</v>
@@ -8388,6 +8547,9 @@
       </c>
       <c r="W98" t="n">
         <v>-1</v>
+      </c>
+      <c r="X98" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -8427,10 +8589,8 @@
       <c r="L99" t="n">
         <v>5</v>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M99" t="n">
+        <v>1</v>
       </c>
       <c r="N99" t="n">
         <v>0</v>
@@ -8469,6 +8629,9 @@
       </c>
       <c r="W99" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X99" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -8508,10 +8671,8 @@
       <c r="L100" t="n">
         <v>5</v>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M100" t="n">
+        <v>4</v>
       </c>
       <c r="N100" t="n">
         <v>2</v>
@@ -8550,6 +8711,9 @@
       </c>
       <c r="W100" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X100" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -8589,10 +8753,8 @@
       <c r="L101" t="n">
         <v>3</v>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M101" t="n">
+        <v>1</v>
       </c>
       <c r="N101" t="n">
         <v>2</v>
@@ -8631,6 +8793,9 @@
       </c>
       <c r="W101" t="n">
         <v>-1</v>
+      </c>
+      <c r="X101" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8670,10 +8835,8 @@
       <c r="L102" t="n">
         <v>5</v>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M102" t="n">
+        <v>4</v>
       </c>
       <c r="N102" t="n">
         <v>2</v>
@@ -8712,6 +8875,9 @@
       </c>
       <c r="W102" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X102" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -8794,6 +8960,9 @@
       <c r="W103" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8875,6 +9044,9 @@
       <c r="W104" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X104" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8913,10 +9085,8 @@
       <c r="L105" t="n">
         <v>5</v>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M105" t="n">
+        <v>5</v>
       </c>
       <c r="N105" t="n">
         <v>2</v>
@@ -8955,6 +9125,9 @@
       </c>
       <c r="W105" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X105" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -8994,10 +9167,8 @@
       <c r="L106" t="n">
         <v>4</v>
       </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M106" t="n">
+        <v>1</v>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -9036,6 +9207,9 @@
       </c>
       <c r="W106" t="n">
         <v>-1</v>
+      </c>
+      <c r="X106" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -9075,10 +9249,8 @@
       <c r="L107" t="n">
         <v>3</v>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M107" t="n">
+        <v>4</v>
       </c>
       <c r="N107" t="n">
         <v>2</v>
@@ -9117,6 +9289,9 @@
       </c>
       <c r="W107" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X107" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -9156,10 +9331,8 @@
       <c r="L108" t="n">
         <v>2</v>
       </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M108" t="n">
+        <v>4</v>
       </c>
       <c r="N108" t="n">
         <v>2</v>
@@ -9198,6 +9371,9 @@
       </c>
       <c r="W108" t="n">
         <v>-1</v>
+      </c>
+      <c r="X108" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -9237,10 +9413,8 @@
       <c r="L109" t="n">
         <v>4</v>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M109" t="n">
+        <v>4</v>
       </c>
       <c r="N109" t="n">
         <v>2</v>
@@ -9279,6 +9453,9 @@
       </c>
       <c r="W109" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X109" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -9318,10 +9495,8 @@
       <c r="L110" t="n">
         <v>4</v>
       </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M110" t="n">
+        <v>5</v>
       </c>
       <c r="N110" t="n">
         <v>1</v>
@@ -9360,6 +9535,9 @@
       </c>
       <c r="W110" t="n">
         <v>-1</v>
+      </c>
+      <c r="X110" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -9399,10 +9577,8 @@
       <c r="L111" t="n">
         <v>3</v>
       </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M111" t="n">
+        <v>4</v>
       </c>
       <c r="N111" t="n">
         <v>2</v>
@@ -9441,6 +9617,9 @@
       </c>
       <c r="W111" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X111" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -9480,10 +9659,8 @@
       <c r="L112" t="n">
         <v>1</v>
       </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M112" t="n">
+        <v>4</v>
       </c>
       <c r="N112" t="n">
         <v>3</v>
@@ -9522,6 +9699,9 @@
       </c>
       <c r="W112" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X112" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -9561,10 +9741,8 @@
       <c r="L113" t="n">
         <v>5</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M113" t="n">
+        <v>1</v>
       </c>
       <c r="N113" t="n">
         <v>2</v>
@@ -9603,6 +9781,9 @@
       </c>
       <c r="W113" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X113" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -9685,6 +9866,9 @@
       <c r="W114" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X114" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9723,10 +9907,8 @@
       <c r="L115" t="n">
         <v>4</v>
       </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M115" t="n">
+        <v>4</v>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -9765,6 +9947,9 @@
       </c>
       <c r="W115" t="n">
         <v>1</v>
+      </c>
+      <c r="X115" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -9847,6 +10032,9 @@
       <c r="W116" t="n">
         <v>-1</v>
       </c>
+      <c r="X116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9885,10 +10073,8 @@
       <c r="L117" t="n">
         <v>4</v>
       </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M117" t="n">
+        <v>5</v>
       </c>
       <c r="N117" t="n">
         <v>2</v>
@@ -9927,6 +10113,9 @@
       </c>
       <c r="W117" t="n">
         <v>-1</v>
+      </c>
+      <c r="X117" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -10009,6 +10198,9 @@
       <c r="W118" t="n">
         <v>1</v>
       </c>
+      <c r="X118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10090,6 +10282,9 @@
       <c r="W119" t="n">
         <v>1</v>
       </c>
+      <c r="X119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10128,10 +10323,8 @@
       <c r="L120" t="n">
         <v>4</v>
       </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M120" t="n">
+        <v>4</v>
       </c>
       <c r="N120" t="n">
         <v>2</v>
@@ -10170,6 +10363,9 @@
       </c>
       <c r="W120" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X120" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -10209,10 +10405,8 @@
       <c r="L121" t="n">
         <v>4</v>
       </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M121" t="n">
+        <v>4</v>
       </c>
       <c r="N121" t="n">
         <v>2</v>
@@ -10251,6 +10445,9 @@
       </c>
       <c r="W121" t="n">
         <v>-1</v>
+      </c>
+      <c r="X121" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -10290,10 +10487,8 @@
       <c r="L122" t="n">
         <v>2</v>
       </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M122" t="n">
+        <v>4</v>
       </c>
       <c r="N122" t="n">
         <v>2</v>
@@ -10331,6 +10526,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W122" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10371,10 +10569,8 @@
       <c r="L123" t="n">
         <v>4</v>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M123" t="n">
+        <v>4</v>
       </c>
       <c r="N123" t="n">
         <v>2</v>
@@ -10413,6 +10609,9 @@
       </c>
       <c r="W123" t="n">
         <v>-1</v>
+      </c>
+      <c r="X123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -10495,6 +10694,9 @@
       <c r="W124" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10533,10 +10735,8 @@
       <c r="L125" t="n">
         <v>5</v>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M125" t="n">
+        <v>1</v>
       </c>
       <c r="N125" t="n">
         <v>3</v>
@@ -10575,6 +10775,9 @@
       </c>
       <c r="W125" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X125" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -10614,10 +10817,8 @@
       <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M126" t="n">
+        <v>4</v>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -10656,6 +10857,9 @@
       </c>
       <c r="W126" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X126" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -10738,6 +10942,9 @@
       <c r="W127" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10819,6 +11026,9 @@
       <c r="W128" t="n">
         <v>1</v>
       </c>
+      <c r="X128" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10857,10 +11067,8 @@
       <c r="L129" t="n">
         <v>4</v>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M129" t="n">
+        <v>4</v>
       </c>
       <c r="N129" t="n">
         <v>2</v>
@@ -10899,6 +11107,9 @@
       </c>
       <c r="W129" t="n">
         <v>1</v>
+      </c>
+      <c r="X129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -10938,10 +11149,8 @@
       <c r="L130" t="n">
         <v>2</v>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M130" t="n">
+        <v>5</v>
       </c>
       <c r="N130" t="n">
         <v>2</v>
@@ -10980,6 +11189,9 @@
       </c>
       <c r="W130" t="n">
         <v>1</v>
+      </c>
+      <c r="X130" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -11019,10 +11231,8 @@
       <c r="L131" t="n">
         <v>4</v>
       </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M131" t="n">
+        <v>4</v>
       </c>
       <c r="N131" t="n">
         <v>2</v>
@@ -11061,6 +11271,9 @@
       </c>
       <c r="W131" t="n">
         <v>-1</v>
+      </c>
+      <c r="X131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -11100,10 +11313,8 @@
       <c r="L132" t="n">
         <v>4</v>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M132" t="n">
+        <v>4</v>
       </c>
       <c r="N132" t="n">
         <v>2</v>
@@ -11142,6 +11353,9 @@
       </c>
       <c r="W132" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -11224,6 +11438,9 @@
       <c r="W133" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X133" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11305,6 +11522,9 @@
       <c r="W134" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X134" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11343,10 +11563,8 @@
       <c r="L135" t="n">
         <v>4</v>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M135" t="n">
+        <v>4</v>
       </c>
       <c r="N135" t="n">
         <v>2</v>
@@ -11385,6 +11603,9 @@
       </c>
       <c r="W135" t="n">
         <v>-1</v>
+      </c>
+      <c r="X135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -11424,10 +11645,8 @@
       <c r="L136" t="n">
         <v>4</v>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M136" t="n">
+        <v>5</v>
       </c>
       <c r="N136" t="n">
         <v>2</v>
@@ -11466,6 +11685,9 @@
       </c>
       <c r="W136" t="n">
         <v>1</v>
+      </c>
+      <c r="X136" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -11505,10 +11727,8 @@
       <c r="L137" t="n">
         <v>4</v>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M137" t="n">
+        <v>1</v>
       </c>
       <c r="N137" t="n">
         <v>1</v>
@@ -11547,6 +11767,9 @@
       </c>
       <c r="W137" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X137" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -11629,6 +11852,9 @@
       <c r="W138" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X138" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11667,10 +11893,8 @@
       <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M139" t="n">
+        <v>4</v>
       </c>
       <c r="N139" t="n">
         <v>2</v>
@@ -11709,6 +11933,9 @@
       </c>
       <c r="W139" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -11748,10 +11975,8 @@
       <c r="L140" t="n">
         <v>3</v>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M140" t="n">
+        <v>5</v>
       </c>
       <c r="N140" t="n">
         <v>1</v>
@@ -11790,6 +12015,9 @@
       </c>
       <c r="W140" t="n">
         <v>-1</v>
+      </c>
+      <c r="X140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -11829,10 +12057,8 @@
       <c r="L141" t="n">
         <v>5</v>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M141" t="n">
+        <v>1</v>
       </c>
       <c r="N141" t="n">
         <v>2</v>
@@ -11871,6 +12097,9 @@
       </c>
       <c r="W141" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X141" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -11953,6 +12182,9 @@
       <c r="W142" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X142" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11991,10 +12223,8 @@
       <c r="L143" t="n">
         <v>5</v>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M143" t="n">
+        <v>1</v>
       </c>
       <c r="N143" t="n">
         <v>2</v>
@@ -12033,6 +12263,9 @@
       </c>
       <c r="W143" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X143" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -12072,10 +12305,8 @@
       <c r="L144" t="n">
         <v>4</v>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M144" t="n">
+        <v>5</v>
       </c>
       <c r="N144" t="n">
         <v>2</v>
@@ -12114,6 +12345,9 @@
       </c>
       <c r="W144" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X144" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -12153,10 +12387,8 @@
       <c r="L145" t="n">
         <v>3</v>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M145" t="n">
+        <v>5</v>
       </c>
       <c r="N145" t="n">
         <v>2</v>
@@ -12195,6 +12427,9 @@
       </c>
       <c r="W145" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X145" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -12277,6 +12512,9 @@
       <c r="W146" t="n">
         <v>-1</v>
       </c>
+      <c r="X146" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -12315,10 +12553,8 @@
       <c r="L147" t="n">
         <v>4</v>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M147" t="n">
+        <v>5</v>
       </c>
       <c r="N147" t="n">
         <v>2</v>
@@ -12357,6 +12593,9 @@
       </c>
       <c r="W147" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X147" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -12396,10 +12635,8 @@
       <c r="L148" t="n">
         <v>2</v>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M148" t="n">
+        <v>4</v>
       </c>
       <c r="N148" t="n">
         <v>2</v>
@@ -12438,6 +12675,9 @@
       </c>
       <c r="W148" t="n">
         <v>1</v>
+      </c>
+      <c r="X148" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -12477,10 +12717,8 @@
       <c r="L149" t="n">
         <v>4</v>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M149" t="n">
+        <v>4</v>
       </c>
       <c r="N149" t="n">
         <v>2</v>
@@ -12519,6 +12757,9 @@
       </c>
       <c r="W149" t="n">
         <v>-1</v>
+      </c>
+      <c r="X149" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -12558,10 +12799,8 @@
       <c r="L150" t="n">
         <v>4</v>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M150" t="n">
+        <v>4</v>
       </c>
       <c r="N150" t="n">
         <v>1</v>
@@ -12600,6 +12839,9 @@
       </c>
       <c r="W150" t="n">
         <v>1</v>
+      </c>
+      <c r="X150" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -12639,10 +12881,8 @@
       <c r="L151" t="n">
         <v>4</v>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M151" t="n">
+        <v>4</v>
       </c>
       <c r="N151" t="n">
         <v>2</v>
@@ -12681,6 +12921,9 @@
       </c>
       <c r="W151" t="n">
         <v>-1</v>
+      </c>
+      <c r="X151" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -12720,10 +12963,8 @@
       <c r="L152" t="n">
         <v>5</v>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M152" t="n">
+        <v>4</v>
       </c>
       <c r="N152" t="n">
         <v>1</v>
@@ -12762,6 +13003,9 @@
       </c>
       <c r="W152" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X152" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -12801,10 +13045,8 @@
       <c r="L153" t="n">
         <v>3</v>
       </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M153" t="n">
+        <v>4</v>
       </c>
       <c r="N153" t="n">
         <v>1</v>
@@ -12843,6 +13085,9 @@
       </c>
       <c r="W153" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X153" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -12882,10 +13127,8 @@
       <c r="L154" t="n">
         <v>4</v>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M154" t="n">
+        <v>4</v>
       </c>
       <c r="N154" t="n">
         <v>1</v>
@@ -12924,6 +13167,9 @@
       </c>
       <c r="W154" t="n">
         <v>-1</v>
+      </c>
+      <c r="X154" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -12963,10 +13209,8 @@
       <c r="L155" t="n">
         <v>2</v>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M155" t="n">
+        <v>5</v>
       </c>
       <c r="N155" t="n">
         <v>2</v>
@@ -13005,6 +13249,9 @@
       </c>
       <c r="W155" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X155" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -13087,6 +13334,9 @@
       <c r="W156" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X156" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13125,10 +13375,8 @@
       <c r="L157" t="n">
         <v>2</v>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M157" t="n">
+        <v>4</v>
       </c>
       <c r="N157" t="n">
         <v>2</v>
@@ -13167,6 +13415,9 @@
       </c>
       <c r="W157" t="n">
         <v>-1</v>
+      </c>
+      <c r="X157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -13249,6 +13500,9 @@
       <c r="W158" t="n">
         <v>-1</v>
       </c>
+      <c r="X158" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -13330,6 +13584,9 @@
       <c r="W159" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X159" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -13368,10 +13625,8 @@
       <c r="L160" t="n">
         <v>2</v>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M160" t="n">
+        <v>5</v>
       </c>
       <c r="N160" t="n">
         <v>2</v>
@@ -13410,6 +13665,9 @@
       </c>
       <c r="W160" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X160" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -13449,10 +13707,8 @@
       <c r="L161" t="n">
         <v>4</v>
       </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M161" t="n">
+        <v>4</v>
       </c>
       <c r="N161" t="n">
         <v>2</v>
@@ -13491,6 +13747,9 @@
       </c>
       <c r="W161" t="n">
         <v>-1</v>
+      </c>
+      <c r="X161" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -13573,6 +13832,9 @@
       <c r="W162" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X162" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -13611,10 +13873,8 @@
       <c r="L163" t="n">
         <v>3</v>
       </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M163" t="n">
+        <v>4</v>
       </c>
       <c r="N163" t="n">
         <v>2</v>
@@ -13653,6 +13913,9 @@
       </c>
       <c r="W163" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X163" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -13692,10 +13955,8 @@
       <c r="L164" t="n">
         <v>4</v>
       </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M164" t="n">
+        <v>4</v>
       </c>
       <c r="N164" t="n">
         <v>2</v>
@@ -13734,6 +13995,9 @@
       </c>
       <c r="W164" t="n">
         <v>-1</v>
+      </c>
+      <c r="X164" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -13773,10 +14037,8 @@
       <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M165" t="n">
+        <v>3</v>
       </c>
       <c r="N165" t="n">
         <v>2</v>
@@ -13815,6 +14077,9 @@
       </c>
       <c r="W165" t="n">
         <v>1</v>
+      </c>
+      <c r="X165" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -13854,10 +14119,8 @@
       <c r="L166" t="n">
         <v>5</v>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M166" t="n">
+        <v>1</v>
       </c>
       <c r="N166" t="n">
         <v>1</v>
@@ -13896,6 +14159,9 @@
       </c>
       <c r="W166" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X166" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -13935,10 +14201,8 @@
       <c r="L167" t="n">
         <v>4</v>
       </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M167" t="n">
+        <v>4</v>
       </c>
       <c r="N167" t="n">
         <v>2</v>
@@ -13977,6 +14241,9 @@
       </c>
       <c r="W167" t="n">
         <v>-1</v>
+      </c>
+      <c r="X167" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -14016,10 +14283,8 @@
       <c r="L168" t="n">
         <v>4</v>
       </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M168" t="n">
+        <v>3</v>
       </c>
       <c r="N168" t="n">
         <v>1</v>
@@ -14058,6 +14323,9 @@
       </c>
       <c r="W168" t="n">
         <v>-1</v>
+      </c>
+      <c r="X168" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -14140,6 +14408,9 @@
       <c r="W169" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X169" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -14221,6 +14492,9 @@
       <c r="W170" t="n">
         <v>-0.7071067811865477</v>
       </c>
+      <c r="X170" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -14259,10 +14533,8 @@
       <c r="L171" t="n">
         <v>2</v>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M171" t="n">
+        <v>5</v>
       </c>
       <c r="N171" t="n">
         <v>2</v>
@@ -14301,6 +14573,9 @@
       </c>
       <c r="W171" t="n">
         <v>-1</v>
+      </c>
+      <c r="X171" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -14340,10 +14615,8 @@
       <c r="L172" t="n">
         <v>5</v>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M172" t="n">
+        <v>4</v>
       </c>
       <c r="N172" t="n">
         <v>1</v>
@@ -14382,6 +14655,9 @@
       </c>
       <c r="W172" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X172" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -14421,10 +14697,8 @@
       <c r="L173" t="n">
         <v>4</v>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M173" t="n">
+        <v>3</v>
       </c>
       <c r="N173" t="n">
         <v>2</v>
@@ -14463,6 +14737,9 @@
       </c>
       <c r="W173" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X173" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -14502,10 +14779,8 @@
       <c r="L174" t="n">
         <v>4</v>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M174" t="n">
+        <v>4</v>
       </c>
       <c r="N174" t="n">
         <v>2</v>
@@ -14544,6 +14819,9 @@
       </c>
       <c r="W174" t="n">
         <v>-1</v>
+      </c>
+      <c r="X174" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -14583,10 +14861,8 @@
       <c r="L175" t="n">
         <v>4</v>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M175" t="n">
+        <v>4</v>
       </c>
       <c r="N175" t="n">
         <v>2</v>
@@ -14625,6 +14901,9 @@
       </c>
       <c r="W175" t="n">
         <v>-1</v>
+      </c>
+      <c r="X175" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -14664,10 +14943,8 @@
       <c r="L176" t="n">
         <v>5</v>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M176" t="n">
+        <v>4</v>
       </c>
       <c r="N176" t="n">
         <v>2</v>
@@ -14706,6 +14983,9 @@
       </c>
       <c r="W176" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X176" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -14745,10 +15025,8 @@
       <c r="L177" t="n">
         <v>5</v>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M177" t="n">
+        <v>5</v>
       </c>
       <c r="N177" t="n">
         <v>1</v>
@@ -14787,6 +15065,9 @@
       </c>
       <c r="W177" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X177" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -14826,10 +15107,8 @@
       <c r="L178" t="n">
         <v>5</v>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M178" t="n">
+        <v>5</v>
       </c>
       <c r="N178" t="n">
         <v>1</v>
@@ -14868,6 +15147,9 @@
       </c>
       <c r="W178" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X178" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -14907,10 +15189,8 @@
       <c r="L179" t="n">
         <v>4</v>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M179" t="n">
+        <v>1</v>
       </c>
       <c r="N179" t="n">
         <v>1</v>
@@ -14949,6 +15229,9 @@
       </c>
       <c r="W179" t="n">
         <v>-1</v>
+      </c>
+      <c r="X179" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -15031,6 +15314,9 @@
       <c r="W180" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X180" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -15069,10 +15355,8 @@
       <c r="L181" t="n">
         <v>5</v>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M181" t="n">
+        <v>5</v>
       </c>
       <c r="N181" t="n">
         <v>2</v>
@@ -15111,6 +15395,9 @@
       </c>
       <c r="W181" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X181" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -15193,6 +15480,9 @@
       <c r="W182" t="n">
         <v>-1</v>
       </c>
+      <c r="X182" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -15231,10 +15521,8 @@
       <c r="L183" t="n">
         <v>5</v>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M183" t="n">
+        <v>5</v>
       </c>
       <c r="N183" t="n">
         <v>2</v>
@@ -15273,6 +15561,9 @@
       </c>
       <c r="W183" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X183" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -15312,10 +15603,8 @@
       <c r="L184" t="n">
         <v>4</v>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M184" t="n">
+        <v>5</v>
       </c>
       <c r="N184" t="n">
         <v>2</v>
@@ -15354,6 +15643,9 @@
       </c>
       <c r="W184" t="n">
         <v>-1</v>
+      </c>
+      <c r="X184" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -15393,10 +15685,8 @@
       <c r="L185" t="n">
         <v>4</v>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M185" t="n">
+        <v>5</v>
       </c>
       <c r="N185" t="n">
         <v>2</v>
@@ -15435,6 +15725,9 @@
       </c>
       <c r="W185" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X185" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -15474,10 +15767,8 @@
       <c r="L186" t="n">
         <v>4</v>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M186" t="n">
+        <v>5</v>
       </c>
       <c r="N186" t="n">
         <v>2</v>
@@ -15516,6 +15807,9 @@
       </c>
       <c r="W186" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X186" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -15598,6 +15892,9 @@
       <c r="W187" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X187" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -15636,10 +15933,8 @@
       <c r="L188" t="n">
         <v>3</v>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M188" t="n">
+        <v>4</v>
       </c>
       <c r="N188" t="n">
         <v>3</v>
@@ -15678,6 +15973,9 @@
       </c>
       <c r="W188" t="n">
         <v>-1</v>
+      </c>
+      <c r="X188" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -15717,10 +16015,8 @@
       <c r="L189" t="n">
         <v>4</v>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M189" t="n">
+        <v>5</v>
       </c>
       <c r="N189" t="n">
         <v>2</v>
@@ -15759,6 +16055,9 @@
       </c>
       <c r="W189" t="n">
         <v>-1</v>
+      </c>
+      <c r="X189" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -15841,6 +16140,9 @@
       <c r="W190" t="n">
         <v>1</v>
       </c>
+      <c r="X190" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -15922,6 +16224,9 @@
       <c r="W191" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X191" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -16003,6 +16308,9 @@
       <c r="W192" t="n">
         <v>-1</v>
       </c>
+      <c r="X192" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -16041,10 +16349,8 @@
       <c r="L193" t="n">
         <v>5</v>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M193" t="n">
+        <v>3</v>
       </c>
       <c r="N193" t="n">
         <v>1</v>
@@ -16083,6 +16389,9 @@
       </c>
       <c r="W193" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X193" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -16122,10 +16431,8 @@
       <c r="L194" t="n">
         <v>4</v>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M194" t="n">
+        <v>4</v>
       </c>
       <c r="N194" t="n">
         <v>2</v>
@@ -16164,6 +16471,9 @@
       </c>
       <c r="W194" t="n">
         <v>-1</v>
+      </c>
+      <c r="X194" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -16203,10 +16513,8 @@
       <c r="L195" t="n">
         <v>5</v>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M195" t="n">
+        <v>4</v>
       </c>
       <c r="N195" t="n">
         <v>1</v>
@@ -16245,6 +16553,9 @@
       </c>
       <c r="W195" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X195" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -16284,10 +16595,8 @@
       <c r="L196" t="n">
         <v>4</v>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M196" t="n">
+        <v>4</v>
       </c>
       <c r="N196" t="n">
         <v>3</v>
@@ -16326,6 +16635,9 @@
       </c>
       <c r="W196" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X196" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -16365,10 +16677,8 @@
       <c r="L197" t="n">
         <v>4</v>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M197" t="n">
+        <v>4</v>
       </c>
       <c r="N197" t="n">
         <v>2</v>
@@ -16407,6 +16717,9 @@
       </c>
       <c r="W197" t="n">
         <v>-1</v>
+      </c>
+      <c r="X197" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -16489,6 +16802,9 @@
       <c r="W198" t="n">
         <v>-1</v>
       </c>
+      <c r="X198" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -16527,10 +16843,8 @@
       <c r="L199" t="n">
         <v>2</v>
       </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M199" t="n">
+        <v>4</v>
       </c>
       <c r="N199" t="n">
         <v>2</v>
@@ -16569,6 +16883,9 @@
       </c>
       <c r="W199" t="n">
         <v>1</v>
+      </c>
+      <c r="X199" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -16608,10 +16925,8 @@
       <c r="L200" t="n">
         <v>3</v>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M200" t="n">
+        <v>5</v>
       </c>
       <c r="N200" t="n">
         <v>2</v>
@@ -16650,6 +16965,9 @@
       </c>
       <c r="W200" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X200" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -16689,10 +17007,8 @@
       <c r="L201" t="n">
         <v>2</v>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M201" t="n">
+        <v>4</v>
       </c>
       <c r="N201" t="n">
         <v>2</v>
@@ -16731,6 +17047,9 @@
       </c>
       <c r="W201" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X201" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -16813,6 +17132,9 @@
       <c r="W202" t="n">
         <v>-1</v>
       </c>
+      <c r="X202" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -16851,10 +17173,8 @@
       <c r="L203" t="n">
         <v>3</v>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M203" t="n">
+        <v>1</v>
       </c>
       <c r="N203" t="n">
         <v>1</v>
@@ -16893,6 +17213,9 @@
       </c>
       <c r="W203" t="n">
         <v>-1</v>
+      </c>
+      <c r="X203" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -16975,6 +17298,9 @@
       <c r="W204" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X204" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -17013,10 +17339,8 @@
       <c r="L205" t="n">
         <v>4</v>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M205" t="n">
+        <v>4</v>
       </c>
       <c r="N205" t="n">
         <v>2</v>
@@ -17055,6 +17379,9 @@
       </c>
       <c r="W205" t="n">
         <v>1</v>
+      </c>
+      <c r="X205" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -17137,6 +17464,9 @@
       <c r="W206" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X206" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -17218,6 +17548,9 @@
       <c r="W207" t="n">
         <v>-1</v>
       </c>
+      <c r="X207" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -17299,6 +17632,9 @@
       <c r="W208" t="n">
         <v>-1</v>
       </c>
+      <c r="X208" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -17337,10 +17673,8 @@
       <c r="L209" t="n">
         <v>3</v>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M209" t="n">
+        <v>5</v>
       </c>
       <c r="N209" t="n">
         <v>2</v>
@@ -17379,6 +17713,9 @@
       </c>
       <c r="W209" t="n">
         <v>-1</v>
+      </c>
+      <c r="X209" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -17418,10 +17755,8 @@
       <c r="L210" t="n">
         <v>2</v>
       </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M210" t="n">
+        <v>5</v>
       </c>
       <c r="N210" t="n">
         <v>2</v>
@@ -17460,6 +17795,9 @@
       </c>
       <c r="W210" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X210" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -17499,10 +17837,8 @@
       <c r="L211" t="n">
         <v>4</v>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M211" t="n">
+        <v>4</v>
       </c>
       <c r="N211" t="n">
         <v>2</v>
@@ -17541,6 +17877,9 @@
       </c>
       <c r="W211" t="n">
         <v>-1</v>
+      </c>
+      <c r="X211" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -17623,6 +17962,9 @@
       <c r="W212" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X212" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -17661,10 +18003,8 @@
       <c r="L213" t="n">
         <v>2</v>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M213" t="n">
+        <v>4</v>
       </c>
       <c r="N213" t="n">
         <v>3</v>
@@ -17703,6 +18043,9 @@
       </c>
       <c r="W213" t="n">
         <v>-1</v>
+      </c>
+      <c r="X213" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -17742,10 +18085,8 @@
       <c r="L214" t="n">
         <v>5</v>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M214" t="n">
+        <v>4</v>
       </c>
       <c r="N214" t="n">
         <v>2</v>
@@ -17784,6 +18125,9 @@
       </c>
       <c r="W214" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X214" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -17823,10 +18167,8 @@
       <c r="L215" t="n">
         <v>5</v>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M215" t="n">
+        <v>5</v>
       </c>
       <c r="N215" t="n">
         <v>2</v>
@@ -17865,6 +18207,9 @@
       </c>
       <c r="W215" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X215" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -17947,6 +18292,9 @@
       <c r="W216" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X216" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -18028,6 +18376,9 @@
       <c r="W217" t="n">
         <v>1</v>
       </c>
+      <c r="X217" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -18066,10 +18417,8 @@
       <c r="L218" t="n">
         <v>5</v>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M218" t="n">
+        <v>4</v>
       </c>
       <c r="N218" t="n">
         <v>2</v>
@@ -18108,6 +18457,9 @@
       </c>
       <c r="W218" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X218" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -18190,6 +18542,9 @@
       <c r="W219" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X219" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -18228,10 +18583,8 @@
       <c r="L220" t="n">
         <v>4</v>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M220" t="n">
+        <v>1</v>
       </c>
       <c r="N220" t="n">
         <v>2</v>
@@ -18270,6 +18623,9 @@
       </c>
       <c r="W220" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X220" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -18352,6 +18708,9 @@
       <c r="W221" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X221" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -18433,6 +18792,9 @@
       <c r="W222" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X222" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -18471,10 +18833,8 @@
       <c r="L223" t="n">
         <v>5</v>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M223" t="n">
+        <v>1</v>
       </c>
       <c r="N223" t="n">
         <v>2</v>
@@ -18513,6 +18873,9 @@
       </c>
       <c r="W223" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X223" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -18552,10 +18915,8 @@
       <c r="L224" t="n">
         <v>5</v>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M224" t="n">
+        <v>4</v>
       </c>
       <c r="N224" t="n">
         <v>2</v>
@@ -18594,6 +18955,9 @@
       </c>
       <c r="W224" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X224" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -18633,10 +18997,8 @@
       <c r="L225" t="n">
         <v>4</v>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M225" t="n">
+        <v>5</v>
       </c>
       <c r="N225" t="n">
         <v>2</v>
@@ -18674,6 +19036,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W225" t="n">
+        <v>1</v>
+      </c>
+      <c r="X225" t="b">
         <v>1</v>
       </c>
     </row>
@@ -18714,10 +19079,8 @@
       <c r="L226" t="n">
         <v>5</v>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M226" t="n">
+        <v>1</v>
       </c>
       <c r="N226" t="n">
         <v>1</v>
@@ -18756,6 +19119,9 @@
       </c>
       <c r="W226" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X226" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -18795,10 +19161,8 @@
       <c r="L227" t="n">
         <v>4</v>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M227" t="n">
+        <v>4</v>
       </c>
       <c r="N227" t="n">
         <v>2</v>
@@ -18837,6 +19201,9 @@
       </c>
       <c r="W227" t="n">
         <v>-1</v>
+      </c>
+      <c r="X227" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -18919,6 +19286,9 @@
       <c r="W228" t="n">
         <v>-1</v>
       </c>
+      <c r="X228" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -18957,10 +19327,8 @@
       <c r="L229" t="n">
         <v>3</v>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M229" t="n">
+        <v>4</v>
       </c>
       <c r="N229" t="n">
         <v>3</v>
@@ -18999,6 +19367,9 @@
       </c>
       <c r="W229" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X229" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -19038,10 +19409,8 @@
       <c r="L230" t="n">
         <v>5</v>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M230" t="n">
+        <v>5</v>
       </c>
       <c r="N230" t="n">
         <v>2</v>
@@ -19080,6 +19449,9 @@
       </c>
       <c r="W230" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X230" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -19162,6 +19534,9 @@
       <c r="W231" t="n">
         <v>-1</v>
       </c>
+      <c r="X231" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -19243,6 +19618,9 @@
       <c r="W232" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X232" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -19281,10 +19659,8 @@
       <c r="L233" t="n">
         <v>5</v>
       </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M233" t="n">
+        <v>4</v>
       </c>
       <c r="N233" t="n">
         <v>2</v>
@@ -19323,6 +19699,9 @@
       </c>
       <c r="W233" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X233" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -19362,10 +19741,8 @@
       <c r="L234" t="n">
         <v>2</v>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M234" t="n">
+        <v>4</v>
       </c>
       <c r="N234" t="n">
         <v>2</v>
@@ -19404,6 +19781,9 @@
       </c>
       <c r="W234" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X234" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -19486,6 +19866,9 @@
       <c r="W235" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X235" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -19524,10 +19907,8 @@
       <c r="L236" t="n">
         <v>4</v>
       </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M236" t="n">
+        <v>4</v>
       </c>
       <c r="N236" t="n">
         <v>2</v>
@@ -19566,6 +19947,9 @@
       </c>
       <c r="W236" t="n">
         <v>-0.7071067811865475</v>
+      </c>
+      <c r="X236" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -19605,10 +19989,8 @@
       <c r="L237" t="n">
         <v>5</v>
       </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M237" t="n">
+        <v>5</v>
       </c>
       <c r="N237" t="n">
         <v>2</v>
@@ -19647,6 +20029,9 @@
       </c>
       <c r="W237" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X237" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -19686,10 +20071,8 @@
       <c r="L238" t="n">
         <v>4</v>
       </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M238" t="n">
+        <v>4</v>
       </c>
       <c r="N238" t="n">
         <v>2</v>
@@ -19728,6 +20111,9 @@
       </c>
       <c r="W238" t="n">
         <v>-1</v>
+      </c>
+      <c r="X238" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -19767,10 +20153,8 @@
       <c r="L239" t="n">
         <v>3</v>
       </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M239" t="n">
+        <v>4</v>
       </c>
       <c r="N239" t="n">
         <v>3</v>
@@ -19809,6 +20193,9 @@
       </c>
       <c r="W239" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X239" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -19848,10 +20235,8 @@
       <c r="L240" t="n">
         <v>5</v>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M240" t="n">
+        <v>4</v>
       </c>
       <c r="N240" t="n">
         <v>2</v>
@@ -19890,6 +20275,9 @@
       </c>
       <c r="W240" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X240" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -19929,10 +20317,8 @@
       <c r="L241" t="n">
         <v>3</v>
       </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M241" t="n">
+        <v>4</v>
       </c>
       <c r="N241" t="n">
         <v>2</v>
@@ -19971,6 +20357,9 @@
       </c>
       <c r="W241" t="n">
         <v>-1</v>
+      </c>
+      <c r="X241" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -20010,10 +20399,8 @@
       <c r="L242" t="n">
         <v>2</v>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M242" t="n">
+        <v>5</v>
       </c>
       <c r="N242" t="n">
         <v>2</v>
@@ -20052,6 +20439,9 @@
       </c>
       <c r="W242" t="n">
         <v>-1</v>
+      </c>
+      <c r="X242" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -20134,6 +20524,9 @@
       <c r="W243" t="n">
         <v>1</v>
       </c>
+      <c r="X243" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -20172,10 +20565,8 @@
       <c r="L244" t="n">
         <v>4</v>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M244" t="n">
+        <v>4</v>
       </c>
       <c r="N244" t="n">
         <v>2</v>
@@ -20214,6 +20605,9 @@
       </c>
       <c r="W244" t="n">
         <v>-1</v>
+      </c>
+      <c r="X244" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -20253,10 +20647,8 @@
       <c r="L245" t="n">
         <v>5</v>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M245" t="n">
+        <v>4</v>
       </c>
       <c r="N245" t="n">
         <v>2</v>
@@ -20295,6 +20687,9 @@
       </c>
       <c r="W245" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X245" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -20334,10 +20729,8 @@
       <c r="L246" t="n">
         <v>4</v>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M246" t="n">
+        <v>4</v>
       </c>
       <c r="N246" t="n">
         <v>2</v>
@@ -20376,6 +20769,9 @@
       </c>
       <c r="W246" t="n">
         <v>-1</v>
+      </c>
+      <c r="X246" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -20415,10 +20811,8 @@
       <c r="L247" t="n">
         <v>2</v>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M247" t="n">
+        <v>4</v>
       </c>
       <c r="N247" t="n">
         <v>3</v>
@@ -20457,6 +20851,9 @@
       </c>
       <c r="W247" t="n">
         <v>-1</v>
+      </c>
+      <c r="X247" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -20539,6 +20936,9 @@
       <c r="W248" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X248" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -20620,6 +21020,9 @@
       <c r="W249" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X249" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -20658,10 +21061,8 @@
       <c r="L250" t="n">
         <v>5</v>
       </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M250" t="n">
+        <v>1</v>
       </c>
       <c r="N250" t="n">
         <v>2</v>
@@ -20700,6 +21101,9 @@
       </c>
       <c r="W250" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X250" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -20739,10 +21143,8 @@
       <c r="L251" t="n">
         <v>4</v>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M251" t="n">
+        <v>1</v>
       </c>
       <c r="N251" t="n">
         <v>1</v>
@@ -20781,6 +21183,9 @@
       </c>
       <c r="W251" t="n">
         <v>-1</v>
+      </c>
+      <c r="X251" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -20820,10 +21225,8 @@
       <c r="L252" t="n">
         <v>4</v>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M252" t="n">
+        <v>4</v>
       </c>
       <c r="N252" t="n">
         <v>2</v>
@@ -20861,6 +21264,9 @@
         <v>6.123233995736766e-17</v>
       </c>
       <c r="W252" t="n">
+        <v>1</v>
+      </c>
+      <c r="X252" t="b">
         <v>1</v>
       </c>
     </row>
@@ -20944,6 +21350,9 @@
       <c r="W253" t="n">
         <v>-1</v>
       </c>
+      <c r="X253" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -21025,6 +21434,9 @@
       <c r="W254" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X254" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -21063,10 +21475,8 @@
       <c r="L255" t="n">
         <v>4</v>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M255" t="n">
+        <v>1</v>
       </c>
       <c r="N255" t="n">
         <v>2</v>
@@ -21105,6 +21515,9 @@
       </c>
       <c r="W255" t="n">
         <v>-1</v>
+      </c>
+      <c r="X255" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -21144,10 +21557,8 @@
       <c r="L256" t="n">
         <v>4</v>
       </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M256" t="n">
+        <v>3</v>
       </c>
       <c r="N256" t="n">
         <v>2</v>
@@ -21186,6 +21597,9 @@
       </c>
       <c r="W256" t="n">
         <v>-1</v>
+      </c>
+      <c r="X256" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -21225,10 +21639,8 @@
       <c r="L257" t="n">
         <v>4</v>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M257" t="n">
+        <v>4</v>
       </c>
       <c r="N257" t="n">
         <v>2</v>
@@ -21267,6 +21679,9 @@
       </c>
       <c r="W257" t="n">
         <v>-1</v>
+      </c>
+      <c r="X257" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -21306,10 +21721,8 @@
       <c r="L258" t="n">
         <v>4</v>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M258" t="n">
+        <v>1</v>
       </c>
       <c r="N258" t="n">
         <v>1</v>
@@ -21348,6 +21761,9 @@
       </c>
       <c r="W258" t="n">
         <v>-1</v>
+      </c>
+      <c r="X258" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -21387,10 +21803,8 @@
       <c r="L259" t="n">
         <v>2</v>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M259" t="n">
+        <v>4</v>
       </c>
       <c r="N259" t="n">
         <v>2</v>
@@ -21429,6 +21843,9 @@
       </c>
       <c r="W259" t="n">
         <v>-1</v>
+      </c>
+      <c r="X259" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -21468,10 +21885,8 @@
       <c r="L260" t="n">
         <v>5</v>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M260" t="n">
+        <v>1</v>
       </c>
       <c r="N260" t="n">
         <v>2</v>
@@ -21510,6 +21925,9 @@
       </c>
       <c r="W260" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X260" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -21592,6 +22010,9 @@
       <c r="W261" t="n">
         <v>-1</v>
       </c>
+      <c r="X261" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -21630,10 +22051,8 @@
       <c r="L262" t="n">
         <v>2</v>
       </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="M262" t="n">
+        <v>2</v>
       </c>
       <c r="N262" t="n">
         <v>2</v>
@@ -21672,6 +22091,9 @@
       </c>
       <c r="W262" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X262" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -21711,10 +22133,8 @@
       <c r="L263" t="n">
         <v>1</v>
       </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M263" t="n">
+        <v>4</v>
       </c>
       <c r="N263" t="n">
         <v>3</v>
@@ -21753,6 +22173,9 @@
       </c>
       <c r="W263" t="n">
         <v>-1</v>
+      </c>
+      <c r="X263" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -21792,10 +22215,8 @@
       <c r="L264" t="n">
         <v>3</v>
       </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M264" t="n">
+        <v>1</v>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -21834,6 +22255,9 @@
       </c>
       <c r="W264" t="n">
         <v>-1</v>
+      </c>
+      <c r="X264" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -21916,6 +22340,9 @@
       <c r="W265" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X265" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -21954,10 +22381,8 @@
       <c r="L266" t="n">
         <v>4</v>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M266" t="n">
+        <v>4</v>
       </c>
       <c r="N266" t="n">
         <v>2</v>
@@ -21996,6 +22421,9 @@
       </c>
       <c r="W266" t="n">
         <v>-1</v>
+      </c>
+      <c r="X266" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -22035,10 +22463,8 @@
       <c r="L267" t="n">
         <v>4</v>
       </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M267" t="n">
+        <v>4</v>
       </c>
       <c r="N267" t="n">
         <v>2</v>
@@ -22077,6 +22503,9 @@
       </c>
       <c r="W267" t="n">
         <v>-1</v>
+      </c>
+      <c r="X267" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -22116,10 +22545,8 @@
       <c r="L268" t="n">
         <v>5</v>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="M268" t="n">
+        <v>3</v>
       </c>
       <c r="N268" t="n">
         <v>1</v>
@@ -22158,6 +22585,9 @@
       </c>
       <c r="W268" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X268" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -22197,10 +22627,8 @@
       <c r="L269" t="n">
         <v>5</v>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M269" t="n">
+        <v>4</v>
       </c>
       <c r="N269" t="n">
         <v>2</v>
@@ -22239,6 +22667,9 @@
       </c>
       <c r="W269" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X269" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -22278,10 +22709,8 @@
       <c r="L270" t="n">
         <v>4</v>
       </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M270" t="n">
+        <v>4</v>
       </c>
       <c r="N270" t="n">
         <v>2</v>
@@ -22320,6 +22749,9 @@
       </c>
       <c r="W270" t="n">
         <v>-1</v>
+      </c>
+      <c r="X270" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -22402,6 +22834,9 @@
       <c r="W271" t="n">
         <v>1</v>
       </c>
+      <c r="X271" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -22440,10 +22875,8 @@
       <c r="L272" t="n">
         <v>4</v>
       </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M272" t="n">
+        <v>4</v>
       </c>
       <c r="N272" t="n">
         <v>2</v>
@@ -22482,6 +22915,9 @@
       </c>
       <c r="W272" t="n">
         <v>-1</v>
+      </c>
+      <c r="X272" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -22564,6 +23000,9 @@
       <c r="W273" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X273" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -22602,10 +23041,8 @@
       <c r="L274" t="n">
         <v>2</v>
       </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M274" t="n">
+        <v>4</v>
       </c>
       <c r="N274" t="n">
         <v>2</v>
@@ -22644,6 +23081,9 @@
       </c>
       <c r="W274" t="n">
         <v>1</v>
+      </c>
+      <c r="X274" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -22683,10 +23123,8 @@
       <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M275" t="n">
+        <v>4</v>
       </c>
       <c r="N275" t="n">
         <v>2</v>
@@ -22725,6 +23163,9 @@
       </c>
       <c r="W275" t="n">
         <v>-0.7071067811865477</v>
+      </c>
+      <c r="X275" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -22764,10 +23205,8 @@
       <c r="L276" t="n">
         <v>5</v>
       </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M276" t="n">
+        <v>5</v>
       </c>
       <c r="N276" t="n">
         <v>2</v>
@@ -22806,6 +23245,9 @@
       </c>
       <c r="W276" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X276" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -22845,10 +23287,8 @@
       <c r="L277" t="n">
         <v>2</v>
       </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M277" t="n">
+        <v>5</v>
       </c>
       <c r="N277" t="n">
         <v>2</v>
@@ -22887,6 +23327,9 @@
       </c>
       <c r="W277" t="n">
         <v>0.7071067811865476</v>
+      </c>
+      <c r="X277" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -22969,6 +23412,9 @@
       <c r="W278" t="n">
         <v>-0.7071067811865475</v>
       </c>
+      <c r="X278" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -23007,10 +23453,8 @@
       <c r="L279" t="n">
         <v>1</v>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M279" t="n">
+        <v>1</v>
       </c>
       <c r="N279" t="n">
         <v>0</v>
@@ -23049,6 +23493,9 @@
       </c>
       <c r="W279" t="n">
         <v>-1</v>
+      </c>
+      <c r="X279" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -23131,6 +23578,9 @@
       <c r="W280" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X280" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -23169,10 +23619,8 @@
       <c r="L281" t="n">
         <v>4</v>
       </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M281" t="n">
+        <v>5</v>
       </c>
       <c r="N281" t="n">
         <v>2</v>
@@ -23211,6 +23659,9 @@
       </c>
       <c r="W281" t="n">
         <v>-1</v>
+      </c>
+      <c r="X281" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -23250,10 +23701,8 @@
       <c r="L282" t="n">
         <v>4</v>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M282" t="n">
+        <v>1</v>
       </c>
       <c r="N282" t="n">
         <v>2</v>
@@ -23292,6 +23741,9 @@
       </c>
       <c r="W282" t="n">
         <v>-1</v>
+      </c>
+      <c r="X282" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -23331,10 +23783,8 @@
       <c r="L283" t="n">
         <v>4</v>
       </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M283" t="n">
+        <v>1</v>
       </c>
       <c r="N283" t="n">
         <v>2</v>
@@ -23373,6 +23823,9 @@
       </c>
       <c r="W283" t="n">
         <v>-1</v>
+      </c>
+      <c r="X283" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -23412,10 +23865,8 @@
       <c r="L284" t="n">
         <v>4</v>
       </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M284" t="n">
+        <v>4</v>
       </c>
       <c r="N284" t="n">
         <v>2</v>
@@ -23454,6 +23905,9 @@
       </c>
       <c r="W284" t="n">
         <v>-1</v>
+      </c>
+      <c r="X284" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -23493,10 +23947,8 @@
       <c r="L285" t="n">
         <v>4</v>
       </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M285" t="n">
+        <v>4</v>
       </c>
       <c r="N285" t="n">
         <v>2</v>
@@ -23535,6 +23987,9 @@
       </c>
       <c r="W285" t="n">
         <v>1</v>
+      </c>
+      <c r="X285" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -23574,10 +24029,8 @@
       <c r="L286" t="n">
         <v>5</v>
       </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M286" t="n">
+        <v>5</v>
       </c>
       <c r="N286" t="n">
         <v>2</v>
@@ -23616,6 +24069,9 @@
       </c>
       <c r="W286" t="n">
         <v>-0.9238795325112865</v>
+      </c>
+      <c r="X286" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -23655,10 +24111,8 @@
       <c r="L287" t="n">
         <v>3</v>
       </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M287" t="n">
+        <v>4</v>
       </c>
       <c r="N287" t="n">
         <v>2</v>
@@ -23697,6 +24151,9 @@
       </c>
       <c r="W287" t="n">
         <v>-1</v>
+      </c>
+      <c r="X287" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -23779,6 +24236,9 @@
       <c r="W288" t="n">
         <v>0.7071067811865476</v>
       </c>
+      <c r="X288" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -23860,6 +24320,9 @@
       <c r="W289" t="n">
         <v>-1</v>
       </c>
+      <c r="X289" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -23898,10 +24361,8 @@
       <c r="L290" t="n">
         <v>4</v>
       </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M290" t="n">
+        <v>5</v>
       </c>
       <c r="N290" t="n">
         <v>2</v>
@@ -23940,6 +24401,9 @@
       </c>
       <c r="W290" t="n">
         <v>-1</v>
+      </c>
+      <c r="X290" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -23979,10 +24443,8 @@
       <c r="L291" t="n">
         <v>2</v>
       </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="M291" t="n">
+        <v>5</v>
       </c>
       <c r="N291" t="n">
         <v>1</v>
@@ -24021,6 +24483,9 @@
       </c>
       <c r="W291" t="n">
         <v>-1</v>
+      </c>
+      <c r="X291" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -24103,6 +24568,9 @@
       <c r="W292" t="n">
         <v>-0.9238795325112865</v>
       </c>
+      <c r="X292" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -24141,10 +24609,8 @@
       <c r="L293" t="n">
         <v>3</v>
       </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M293" t="n">
+        <v>4</v>
       </c>
       <c r="N293" t="n">
         <v>2</v>
@@ -24183,6 +24649,9 @@
       </c>
       <c r="W293" t="n">
         <v>-1</v>
+      </c>
+      <c r="X293" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -24222,10 +24691,8 @@
       <c r="L294" t="n">
         <v>4</v>
       </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="M294" t="n">
+        <v>4</v>
       </c>
       <c r="N294" t="n">
         <v>2</v>
@@ -24264,6 +24731,9 @@
       </c>
       <c r="W294" t="n">
         <v>-1</v>
+      </c>
+      <c r="X294" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/split/val.xlsx
+++ b/data/split/val.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X294"/>
+  <dimension ref="A1:Y294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,11 @@
           <t>men</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -616,7 +621,10 @@
       <c r="W2" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X2" t="b">
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -700,8 +708,11 @@
       <c r="W3" t="n">
         <v>-1</v>
       </c>
-      <c r="X3" t="b">
-        <v>0</v>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -782,7 +793,10 @@
       <c r="W4" t="n">
         <v>-1</v>
       </c>
-      <c r="X4" t="b">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,8 +880,11 @@
       <c r="W5" t="n">
         <v>-1</v>
       </c>
-      <c r="X5" t="b">
-        <v>0</v>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -948,8 +965,11 @@
       <c r="W6" t="n">
         <v>-1</v>
       </c>
-      <c r="X6" t="b">
-        <v>0</v>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1032,7 +1052,10 @@
       <c r="W7" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X7" t="b">
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1116,8 +1139,11 @@
       <c r="W8" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1198,8 +1224,11 @@
       <c r="W9" t="n">
         <v>-1</v>
       </c>
-      <c r="X9" t="b">
-        <v>0</v>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1280,8 +1309,11 @@
       <c r="W10" t="n">
         <v>-1</v>
       </c>
-      <c r="X10" t="b">
-        <v>0</v>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1362,8 +1394,11 @@
       <c r="W11" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X11" t="b">
-        <v>1</v>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1444,7 +1479,10 @@
       <c r="W12" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X12" t="b">
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1528,8 +1566,11 @@
       <c r="W13" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X13" t="b">
-        <v>1</v>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1612,7 +1653,10 @@
       <c r="W14" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X14" t="b">
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1694,8 +1738,11 @@
       <c r="W15" t="n">
         <v>-1</v>
       </c>
-      <c r="X15" t="b">
-        <v>1</v>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1776,8 +1823,11 @@
       <c r="W16" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X16" t="b">
-        <v>0</v>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1858,7 +1908,10 @@
       <c r="W17" t="n">
         <v>-1</v>
       </c>
-      <c r="X17" t="b">
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1940,8 +1993,11 @@
       <c r="W18" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X18" t="b">
-        <v>0</v>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2022,7 +2078,10 @@
       <c r="W19" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X19" t="b">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2104,7 +2163,10 @@
       <c r="W20" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X20" t="b">
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2186,8 +2248,11 @@
       <c r="W21" t="n">
         <v>-1</v>
       </c>
-      <c r="X21" t="b">
-        <v>0</v>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2268,8 +2333,11 @@
       <c r="W22" t="n">
         <v>-1</v>
       </c>
-      <c r="X22" t="b">
-        <v>0</v>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2352,7 +2420,10 @@
       <c r="W23" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X23" t="b">
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2434,7 +2505,10 @@
       <c r="W24" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X24" t="b">
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2518,8 +2592,11 @@
       <c r="W25" t="n">
         <v>-1</v>
       </c>
-      <c r="X25" t="b">
-        <v>0</v>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2600,8 +2677,11 @@
       <c r="W26" t="n">
         <v>1</v>
       </c>
-      <c r="X26" t="b">
-        <v>0</v>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2682,8 +2762,11 @@
       <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="X27" t="b">
-        <v>1</v>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2766,8 +2849,11 @@
       <c r="W28" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X28" t="b">
-        <v>0</v>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2848,7 +2934,10 @@
       <c r="W29" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X29" t="b">
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2930,8 +3019,11 @@
       <c r="W30" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X30" t="b">
-        <v>1</v>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3014,7 +3106,10 @@
       <c r="W31" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X31" t="b">
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3096,7 +3191,10 @@
       <c r="W32" t="n">
         <v>-1</v>
       </c>
-      <c r="X32" t="b">
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3178,8 +3276,11 @@
       <c r="W33" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X33" t="b">
-        <v>0</v>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3260,7 +3361,10 @@
       <c r="W34" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X34" t="b">
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3344,7 +3448,10 @@
       <c r="W35" t="n">
         <v>-1</v>
       </c>
-      <c r="X35" t="b">
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3426,7 +3533,10 @@
       <c r="W36" t="n">
         <v>-1</v>
       </c>
-      <c r="X36" t="b">
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3508,8 +3618,11 @@
       <c r="W37" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X37" t="b">
-        <v>0</v>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3592,8 +3705,11 @@
       <c r="W38" t="n">
         <v>-1</v>
       </c>
-      <c r="X38" t="b">
-        <v>0</v>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3676,7 +3792,10 @@
       <c r="W39" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X39" t="b">
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3760,8 +3879,11 @@
       <c r="W40" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X40" t="b">
-        <v>0</v>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3844,7 +3966,10 @@
       <c r="W41" t="n">
         <v>-1</v>
       </c>
-      <c r="X41" t="b">
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3926,7 +4051,10 @@
       <c r="W42" t="n">
         <v>-1</v>
       </c>
-      <c r="X42" t="b">
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4008,7 +4136,10 @@
       <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="X43" t="b">
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4092,8 +4223,11 @@
       <c r="W44" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X44" t="b">
-        <v>1</v>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4174,8 +4308,11 @@
       <c r="W45" t="n">
         <v>-1</v>
       </c>
-      <c r="X45" t="b">
-        <v>0</v>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -4256,8 +4393,11 @@
       <c r="W46" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X46" t="b">
-        <v>1</v>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4340,8 +4480,11 @@
       <c r="W47" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X47" t="b">
-        <v>0</v>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4424,8 +4567,11 @@
       <c r="W48" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X48" t="b">
-        <v>0</v>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4508,8 +4654,11 @@
       <c r="W49" t="n">
         <v>-1</v>
       </c>
-      <c r="X49" t="b">
-        <v>0</v>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4590,7 +4739,10 @@
       <c r="W50" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X50" t="b">
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4672,8 +4824,11 @@
       <c r="W51" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X51" t="b">
-        <v>0</v>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4756,8 +4911,11 @@
       <c r="W52" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X52" t="b">
-        <v>1</v>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4838,8 +4996,11 @@
       <c r="W53" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X53" t="b">
-        <v>1</v>
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4922,8 +5083,11 @@
       <c r="W54" t="n">
         <v>-1</v>
       </c>
-      <c r="X54" t="b">
-        <v>1</v>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5004,8 +5168,11 @@
       <c r="W55" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X55" t="b">
-        <v>1</v>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5088,7 +5255,10 @@
       <c r="W56" t="n">
         <v>-1</v>
       </c>
-      <c r="X56" t="b">
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5170,7 +5340,10 @@
       <c r="W57" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X57" t="b">
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5252,8 +5425,11 @@
       <c r="W58" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X58" t="b">
-        <v>0</v>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -5334,8 +5510,11 @@
       <c r="W59" t="n">
         <v>-1</v>
       </c>
-      <c r="X59" t="b">
-        <v>0</v>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5416,7 +5595,10 @@
       <c r="W60" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X60" t="b">
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5500,7 +5682,10 @@
       <c r="W61" t="n">
         <v>-1</v>
       </c>
-      <c r="X61" t="b">
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5582,8 +5767,11 @@
       <c r="W62" t="n">
         <v>-1</v>
       </c>
-      <c r="X62" t="b">
-        <v>1</v>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5664,7 +5852,10 @@
       <c r="W63" t="n">
         <v>1</v>
       </c>
-      <c r="X63" t="b">
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5746,8 +5937,11 @@
       <c r="W64" t="n">
         <v>1</v>
       </c>
-      <c r="X64" t="b">
-        <v>0</v>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5830,8 +6024,11 @@
       <c r="W65" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X65" t="b">
-        <v>0</v>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5914,7 +6111,10 @@
       <c r="W66" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X66" t="b">
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5996,8 +6196,11 @@
       <c r="W67" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X67" t="b">
-        <v>0</v>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -6078,8 +6281,11 @@
       <c r="W68" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X68" t="b">
-        <v>0</v>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6160,8 +6366,11 @@
       <c r="W69" t="n">
         <v>-1</v>
       </c>
-      <c r="X69" t="b">
-        <v>0</v>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -6242,8 +6451,11 @@
       <c r="W70" t="n">
         <v>-1</v>
       </c>
-      <c r="X70" t="b">
-        <v>0</v>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6324,7 +6536,10 @@
       <c r="W71" t="n">
         <v>-1</v>
       </c>
-      <c r="X71" t="b">
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6408,7 +6623,10 @@
       <c r="W72" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X72" t="b">
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6490,8 +6708,11 @@
       <c r="W73" t="n">
         <v>-1</v>
       </c>
-      <c r="X73" t="b">
-        <v>0</v>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -6574,8 +6795,11 @@
       <c r="W74" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X74" t="b">
-        <v>1</v>
+      <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6656,8 +6880,11 @@
       <c r="W75" t="n">
         <v>-1</v>
       </c>
-      <c r="X75" t="b">
-        <v>1</v>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6738,7 +6965,10 @@
       <c r="W76" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X76" t="b">
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6820,8 +7050,11 @@
       <c r="W77" t="n">
         <v>-1</v>
       </c>
-      <c r="X77" t="b">
-        <v>1</v>
+      <c r="X77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6902,8 +7135,11 @@
       <c r="W78" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X78" t="b">
-        <v>0</v>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6984,7 +7220,10 @@
       <c r="W79" t="n">
         <v>-1</v>
       </c>
-      <c r="X79" t="b">
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7066,8 +7305,11 @@
       <c r="W80" t="n">
         <v>-1</v>
       </c>
-      <c r="X80" t="b">
-        <v>1</v>
+      <c r="X80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -7148,7 +7390,10 @@
       <c r="W81" t="n">
         <v>-1</v>
       </c>
-      <c r="X81" t="b">
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7230,7 +7475,10 @@
       <c r="W82" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X82" t="b">
+      <c r="X82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7312,8 +7560,11 @@
       <c r="W83" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X83" t="b">
-        <v>1</v>
+      <c r="X83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7396,7 +7647,10 @@
       <c r="W84" t="n">
         <v>-1</v>
       </c>
-      <c r="X84" t="b">
+      <c r="X84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7478,7 +7732,10 @@
       <c r="W85" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X85" t="b">
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7560,8 +7817,11 @@
       <c r="W86" t="n">
         <v>-1</v>
       </c>
-      <c r="X86" t="b">
-        <v>0</v>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -7642,7 +7902,10 @@
       <c r="W87" t="n">
         <v>-1</v>
       </c>
-      <c r="X87" t="b">
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7724,8 +7987,11 @@
       <c r="W88" t="n">
         <v>-1</v>
       </c>
-      <c r="X88" t="b">
-        <v>1</v>
+      <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7806,8 +8072,11 @@
       <c r="W89" t="n">
         <v>-1</v>
       </c>
-      <c r="X89" t="b">
-        <v>0</v>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -7890,8 +8159,11 @@
       <c r="W90" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X90" t="b">
-        <v>0</v>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -7972,8 +8244,11 @@
       <c r="W91" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X91" t="b">
-        <v>0</v>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -8054,7 +8329,10 @@
       <c r="W92" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X92" t="b">
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8136,8 +8414,11 @@
       <c r="W93" t="n">
         <v>1</v>
       </c>
-      <c r="X93" t="b">
-        <v>0</v>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -8218,7 +8499,10 @@
       <c r="W94" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X94" t="b">
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8300,8 +8584,11 @@
       <c r="W95" t="n">
         <v>-1</v>
       </c>
-      <c r="X95" t="b">
-        <v>0</v>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -8384,8 +8671,11 @@
       <c r="W96" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X96" t="b">
-        <v>0</v>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -8466,7 +8756,10 @@
       <c r="W97" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X97" t="b">
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8548,7 +8841,10 @@
       <c r="W98" t="n">
         <v>-1</v>
       </c>
-      <c r="X98" t="b">
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8630,7 +8926,10 @@
       <c r="W99" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X99" t="b">
+      <c r="X99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8712,8 +9011,11 @@
       <c r="W100" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X100" t="b">
-        <v>1</v>
+      <c r="X100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -8794,8 +9096,11 @@
       <c r="W101" t="n">
         <v>-1</v>
       </c>
-      <c r="X101" t="b">
-        <v>1</v>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -8876,7 +9181,10 @@
       <c r="W102" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X102" t="b">
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8960,8 +9268,11 @@
       <c r="W103" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X103" t="b">
-        <v>1</v>
+      <c r="X103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -9044,8 +9355,11 @@
       <c r="W104" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X104" t="b">
-        <v>1</v>
+      <c r="X104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -9126,8 +9440,11 @@
       <c r="W105" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X105" t="b">
-        <v>1</v>
+      <c r="X105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -9208,8 +9525,11 @@
       <c r="W106" t="n">
         <v>-1</v>
       </c>
-      <c r="X106" t="b">
-        <v>0</v>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -9290,8 +9610,11 @@
       <c r="W107" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X107" t="b">
-        <v>0</v>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -9372,8 +9695,11 @@
       <c r="W108" t="n">
         <v>-1</v>
       </c>
-      <c r="X108" t="b">
-        <v>1</v>
+      <c r="X108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -9454,7 +9780,10 @@
       <c r="W109" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X109" t="b">
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9536,8 +9865,11 @@
       <c r="W110" t="n">
         <v>-1</v>
       </c>
-      <c r="X110" t="b">
-        <v>0</v>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9618,8 +9950,11 @@
       <c r="W111" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X111" t="b">
-        <v>0</v>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -9700,7 +10035,10 @@
       <c r="W112" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X112" t="b">
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9782,7 +10120,10 @@
       <c r="W113" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X113" t="b">
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9866,8 +10207,11 @@
       <c r="W114" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X114" t="b">
-        <v>1</v>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -9948,8 +10292,11 @@
       <c r="W115" t="n">
         <v>1</v>
       </c>
-      <c r="X115" t="b">
-        <v>0</v>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -10032,7 +10379,10 @@
       <c r="W116" t="n">
         <v>-1</v>
       </c>
-      <c r="X116" t="b">
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10114,8 +10464,11 @@
       <c r="W117" t="n">
         <v>-1</v>
       </c>
-      <c r="X117" t="b">
-        <v>0</v>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -10198,7 +10551,10 @@
       <c r="W118" t="n">
         <v>1</v>
       </c>
-      <c r="X118" t="b">
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10282,7 +10638,10 @@
       <c r="W119" t="n">
         <v>1</v>
       </c>
-      <c r="X119" t="b">
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10364,7 +10723,10 @@
       <c r="W120" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X120" t="b">
+      <c r="X120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10446,8 +10808,11 @@
       <c r="W121" t="n">
         <v>-1</v>
       </c>
-      <c r="X121" t="b">
-        <v>1</v>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10528,7 +10893,10 @@
       <c r="W122" t="n">
         <v>1</v>
       </c>
-      <c r="X122" t="b">
+      <c r="X122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10610,8 +10978,11 @@
       <c r="W123" t="n">
         <v>-1</v>
       </c>
-      <c r="X123" t="b">
-        <v>0</v>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -10694,8 +11065,11 @@
       <c r="W124" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X124" t="b">
-        <v>0</v>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -10776,8 +11150,11 @@
       <c r="W125" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X125" t="b">
-        <v>0</v>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -10858,7 +11235,10 @@
       <c r="W126" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X126" t="b">
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10942,7 +11322,10 @@
       <c r="W127" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X127" t="b">
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11026,7 +11409,10 @@
       <c r="W128" t="n">
         <v>1</v>
       </c>
-      <c r="X128" t="b">
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11108,7 +11494,10 @@
       <c r="W129" t="n">
         <v>1</v>
       </c>
-      <c r="X129" t="b">
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11190,8 +11579,11 @@
       <c r="W130" t="n">
         <v>1</v>
       </c>
-      <c r="X130" t="b">
-        <v>0</v>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -11272,7 +11664,10 @@
       <c r="W131" t="n">
         <v>-1</v>
       </c>
-      <c r="X131" t="b">
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11354,7 +11749,10 @@
       <c r="W132" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X132" t="b">
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11438,7 +11836,10 @@
       <c r="W133" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X133" t="b">
+      <c r="X133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y133" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11522,7 +11923,10 @@
       <c r="W134" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X134" t="b">
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11604,8 +12008,11 @@
       <c r="W135" t="n">
         <v>-1</v>
       </c>
-      <c r="X135" t="b">
-        <v>0</v>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -11686,8 +12093,11 @@
       <c r="W136" t="n">
         <v>1</v>
       </c>
-      <c r="X136" t="b">
-        <v>0</v>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -11768,7 +12178,10 @@
       <c r="W137" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X137" t="b">
+      <c r="X137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y137" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11852,7 +12265,10 @@
       <c r="W138" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X138" t="b">
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y138" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11934,8 +12350,11 @@
       <c r="W139" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X139" t="b">
-        <v>0</v>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -12016,7 +12435,10 @@
       <c r="W140" t="n">
         <v>-1</v>
       </c>
-      <c r="X140" t="b">
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12098,7 +12520,10 @@
       <c r="W141" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X141" t="b">
+      <c r="X141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12182,8 +12607,11 @@
       <c r="W142" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X142" t="b">
-        <v>0</v>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -12264,7 +12692,10 @@
       <c r="W143" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X143" t="b">
+      <c r="X143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12346,8 +12777,11 @@
       <c r="W144" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X144" t="b">
-        <v>1</v>
+      <c r="X144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -12428,8 +12862,11 @@
       <c r="W145" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X145" t="b">
-        <v>1</v>
+      <c r="X145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -12512,8 +12949,11 @@
       <c r="W146" t="n">
         <v>-1</v>
       </c>
-      <c r="X146" t="b">
-        <v>0</v>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -12594,7 +13034,10 @@
       <c r="W147" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X147" t="b">
+      <c r="X147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y147" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12676,7 +13119,10 @@
       <c r="W148" t="n">
         <v>1</v>
       </c>
-      <c r="X148" t="b">
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12758,7 +13204,10 @@
       <c r="W149" t="n">
         <v>-1</v>
       </c>
-      <c r="X149" t="b">
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12840,8 +13289,11 @@
       <c r="W150" t="n">
         <v>1</v>
       </c>
-      <c r="X150" t="b">
-        <v>0</v>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -12922,7 +13374,10 @@
       <c r="W151" t="n">
         <v>-1</v>
       </c>
-      <c r="X151" t="b">
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13004,7 +13459,10 @@
       <c r="W152" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X152" t="b">
+      <c r="X152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13086,7 +13544,10 @@
       <c r="W153" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X153" t="b">
+      <c r="X153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y153" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13168,8 +13629,11 @@
       <c r="W154" t="n">
         <v>-1</v>
       </c>
-      <c r="X154" t="b">
-        <v>0</v>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -13250,8 +13714,11 @@
       <c r="W155" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X155" t="b">
-        <v>1</v>
+      <c r="X155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -13334,7 +13801,10 @@
       <c r="W156" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X156" t="b">
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13416,7 +13886,10 @@
       <c r="W157" t="n">
         <v>-1</v>
       </c>
-      <c r="X157" t="b">
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13500,8 +13973,11 @@
       <c r="W158" t="n">
         <v>-1</v>
       </c>
-      <c r="X158" t="b">
-        <v>0</v>
+      <c r="X158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -13584,7 +14060,10 @@
       <c r="W159" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X159" t="b">
+      <c r="X159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y159" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13666,7 +14145,10 @@
       <c r="W160" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X160" t="b">
+      <c r="X160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13748,8 +14230,11 @@
       <c r="W161" t="n">
         <v>-1</v>
       </c>
-      <c r="X161" t="b">
-        <v>0</v>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -13832,8 +14317,11 @@
       <c r="W162" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X162" t="b">
-        <v>0</v>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -13914,7 +14402,10 @@
       <c r="W163" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X163" t="b">
+      <c r="X163" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y163" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13996,7 +14487,10 @@
       <c r="W164" t="n">
         <v>-1</v>
       </c>
-      <c r="X164" t="b">
+      <c r="X164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14078,7 +14572,10 @@
       <c r="W165" t="n">
         <v>1</v>
       </c>
-      <c r="X165" t="b">
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14160,7 +14657,10 @@
       <c r="W166" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X166" t="b">
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14242,8 +14742,11 @@
       <c r="W167" t="n">
         <v>-1</v>
       </c>
-      <c r="X167" t="b">
-        <v>0</v>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -14324,7 +14827,10 @@
       <c r="W168" t="n">
         <v>-1</v>
       </c>
-      <c r="X168" t="b">
+      <c r="X168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y168" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14408,8 +14914,11 @@
       <c r="W169" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X169" t="b">
-        <v>0</v>
+      <c r="X169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -14492,7 +15001,10 @@
       <c r="W170" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X170" t="b">
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14574,7 +15086,10 @@
       <c r="W171" t="n">
         <v>-1</v>
       </c>
-      <c r="X171" t="b">
+      <c r="X171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14656,8 +15171,11 @@
       <c r="W172" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X172" t="b">
-        <v>0</v>
+      <c r="X172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -14738,7 +15256,10 @@
       <c r="W173" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X173" t="b">
+      <c r="X173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14820,7 +15341,10 @@
       <c r="W174" t="n">
         <v>-1</v>
       </c>
-      <c r="X174" t="b">
+      <c r="X174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14902,8 +15426,11 @@
       <c r="W175" t="n">
         <v>-1</v>
       </c>
-      <c r="X175" t="b">
-        <v>0</v>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -14984,8 +15511,11 @@
       <c r="W176" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X176" t="b">
-        <v>1</v>
+      <c r="X176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -15066,8 +15596,11 @@
       <c r="W177" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X177" t="b">
-        <v>0</v>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -15148,8 +15681,11 @@
       <c r="W178" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X178" t="b">
-        <v>0</v>
+      <c r="X178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -15230,8 +15766,11 @@
       <c r="W179" t="n">
         <v>-1</v>
       </c>
-      <c r="X179" t="b">
-        <v>0</v>
+      <c r="X179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -15314,7 +15853,10 @@
       <c r="W180" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X180" t="b">
+      <c r="X180" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y180" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15396,8 +15938,11 @@
       <c r="W181" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X181" t="b">
-        <v>0</v>
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -15480,7 +16025,10 @@
       <c r="W182" t="n">
         <v>-1</v>
       </c>
-      <c r="X182" t="b">
+      <c r="X182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15562,8 +16110,11 @@
       <c r="W183" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X183" t="b">
-        <v>0</v>
+      <c r="X183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -15644,7 +16195,10 @@
       <c r="W184" t="n">
         <v>-1</v>
       </c>
-      <c r="X184" t="b">
+      <c r="X184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15726,8 +16280,11 @@
       <c r="W185" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X185" t="b">
-        <v>0</v>
+      <c r="X185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -15808,7 +16365,10 @@
       <c r="W186" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X186" t="b">
+      <c r="X186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15892,7 +16452,10 @@
       <c r="W187" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X187" t="b">
+      <c r="X187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15974,7 +16537,10 @@
       <c r="W188" t="n">
         <v>-1</v>
       </c>
-      <c r="X188" t="b">
+      <c r="X188" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y188" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16056,7 +16622,10 @@
       <c r="W189" t="n">
         <v>-1</v>
       </c>
-      <c r="X189" t="b">
+      <c r="X189" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y189" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16140,8 +16709,11 @@
       <c r="W190" t="n">
         <v>1</v>
       </c>
-      <c r="X190" t="b">
-        <v>1</v>
+      <c r="X190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -16224,7 +16796,10 @@
       <c r="W191" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X191" t="b">
+      <c r="X191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16308,8 +16883,11 @@
       <c r="W192" t="n">
         <v>-1</v>
       </c>
-      <c r="X192" t="b">
-        <v>1</v>
+      <c r="X192" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -16390,7 +16968,10 @@
       <c r="W193" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X193" t="b">
+      <c r="X193" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y193" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16472,7 +17053,10 @@
       <c r="W194" t="n">
         <v>-1</v>
       </c>
-      <c r="X194" t="b">
+      <c r="X194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16554,7 +17138,10 @@
       <c r="W195" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X195" t="b">
+      <c r="X195" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16636,7 +17223,10 @@
       <c r="W196" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X196" t="b">
+      <c r="X196" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y196" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16718,7 +17308,10 @@
       <c r="W197" t="n">
         <v>-1</v>
       </c>
-      <c r="X197" t="b">
+      <c r="X197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y197" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16802,8 +17395,11 @@
       <c r="W198" t="n">
         <v>-1</v>
       </c>
-      <c r="X198" t="b">
-        <v>0</v>
+      <c r="X198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -16884,7 +17480,10 @@
       <c r="W199" t="n">
         <v>1</v>
       </c>
-      <c r="X199" t="b">
+      <c r="X199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16966,7 +17565,10 @@
       <c r="W200" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X200" t="b">
+      <c r="X200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17048,7 +17650,10 @@
       <c r="W201" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X201" t="b">
+      <c r="X201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17132,8 +17737,11 @@
       <c r="W202" t="n">
         <v>-1</v>
       </c>
-      <c r="X202" t="b">
-        <v>0</v>
+      <c r="X202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -17214,8 +17822,11 @@
       <c r="W203" t="n">
         <v>-1</v>
       </c>
-      <c r="X203" t="b">
-        <v>1</v>
+      <c r="X203" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -17298,7 +17909,10 @@
       <c r="W204" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X204" t="b">
+      <c r="X204" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y204" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17380,7 +17994,10 @@
       <c r="W205" t="n">
         <v>1</v>
       </c>
-      <c r="X205" t="b">
+      <c r="X205" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y205" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17464,8 +18081,11 @@
       <c r="W206" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X206" t="b">
-        <v>1</v>
+      <c r="X206" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -17548,8 +18168,11 @@
       <c r="W207" t="n">
         <v>-1</v>
       </c>
-      <c r="X207" t="b">
-        <v>1</v>
+      <c r="X207" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -17632,7 +18255,10 @@
       <c r="W208" t="n">
         <v>-1</v>
       </c>
-      <c r="X208" t="b">
+      <c r="X208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17714,7 +18340,10 @@
       <c r="W209" t="n">
         <v>-1</v>
       </c>
-      <c r="X209" t="b">
+      <c r="X209" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y209" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17796,7 +18425,10 @@
       <c r="W210" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X210" t="b">
+      <c r="X210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17878,8 +18510,11 @@
       <c r="W211" t="n">
         <v>-1</v>
       </c>
-      <c r="X211" t="b">
-        <v>0</v>
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -17962,8 +18597,11 @@
       <c r="W212" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X212" t="b">
-        <v>1</v>
+      <c r="X212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -18044,8 +18682,11 @@
       <c r="W213" t="n">
         <v>-1</v>
       </c>
-      <c r="X213" t="b">
-        <v>1</v>
+      <c r="X213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -18126,8 +18767,11 @@
       <c r="W214" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X214" t="b">
-        <v>0</v>
+      <c r="X214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -18208,8 +18852,11 @@
       <c r="W215" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X215" t="b">
-        <v>0</v>
+      <c r="X215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -18292,8 +18939,11 @@
       <c r="W216" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X216" t="b">
-        <v>1</v>
+      <c r="X216" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -18376,7 +19026,10 @@
       <c r="W217" t="n">
         <v>1</v>
       </c>
-      <c r="X217" t="b">
+      <c r="X217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18458,8 +19111,11 @@
       <c r="W218" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X218" t="b">
-        <v>1</v>
+      <c r="X218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -18542,8 +19198,11 @@
       <c r="W219" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X219" t="b">
-        <v>1</v>
+      <c r="X219" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -18624,7 +19283,10 @@
       <c r="W220" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X220" t="b">
+      <c r="X220" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y220" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18708,8 +19370,11 @@
       <c r="W221" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X221" t="b">
-        <v>1</v>
+      <c r="X221" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -18792,8 +19457,11 @@
       <c r="W222" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X222" t="b">
-        <v>0</v>
+      <c r="X222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -18874,7 +19542,10 @@
       <c r="W223" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X223" t="b">
+      <c r="X223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18956,8 +19627,11 @@
       <c r="W224" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X224" t="b">
-        <v>0</v>
+      <c r="X224" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -19038,7 +19712,10 @@
       <c r="W225" t="n">
         <v>1</v>
       </c>
-      <c r="X225" t="b">
+      <c r="X225" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y225" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19120,8 +19797,11 @@
       <c r="W226" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X226" t="b">
-        <v>0</v>
+      <c r="X226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -19202,7 +19882,10 @@
       <c r="W227" t="n">
         <v>-1</v>
       </c>
-      <c r="X227" t="b">
+      <c r="X227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19286,8 +19969,11 @@
       <c r="W228" t="n">
         <v>-1</v>
       </c>
-      <c r="X228" t="b">
-        <v>0</v>
+      <c r="X228" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -19368,8 +20054,11 @@
       <c r="W229" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X229" t="b">
-        <v>1</v>
+      <c r="X229" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -19450,7 +20139,10 @@
       <c r="W230" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X230" t="b">
+      <c r="X230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19534,8 +20226,11 @@
       <c r="W231" t="n">
         <v>-1</v>
       </c>
-      <c r="X231" t="b">
-        <v>1</v>
+      <c r="X231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -19618,7 +20313,10 @@
       <c r="W232" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X232" t="b">
+      <c r="X232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19700,7 +20398,10 @@
       <c r="W233" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X233" t="b">
+      <c r="X233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19782,8 +20483,11 @@
       <c r="W234" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X234" t="b">
-        <v>0</v>
+      <c r="X234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -19866,8 +20570,11 @@
       <c r="W235" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X235" t="b">
-        <v>0</v>
+      <c r="X235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -19948,7 +20655,10 @@
       <c r="W236" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X236" t="b">
+      <c r="X236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20030,7 +20740,10 @@
       <c r="W237" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X237" t="b">
+      <c r="X237" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y237" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20112,7 +20825,10 @@
       <c r="W238" t="n">
         <v>-1</v>
       </c>
-      <c r="X238" t="b">
+      <c r="X238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y238" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20194,7 +20910,10 @@
       <c r="W239" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X239" t="b">
+      <c r="X239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y239" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20276,7 +20995,10 @@
       <c r="W240" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X240" t="b">
+      <c r="X240" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y240" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20358,8 +21080,11 @@
       <c r="W241" t="n">
         <v>-1</v>
       </c>
-      <c r="X241" t="b">
-        <v>0</v>
+      <c r="X241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -20440,7 +21165,10 @@
       <c r="W242" t="n">
         <v>-1</v>
       </c>
-      <c r="X242" t="b">
+      <c r="X242" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y242" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20524,7 +21252,10 @@
       <c r="W243" t="n">
         <v>1</v>
       </c>
-      <c r="X243" t="b">
+      <c r="X243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20606,8 +21337,11 @@
       <c r="W244" t="n">
         <v>-1</v>
       </c>
-      <c r="X244" t="b">
-        <v>0</v>
+      <c r="X244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -20688,8 +21422,11 @@
       <c r="W245" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X245" t="b">
-        <v>0</v>
+      <c r="X245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -20770,8 +21507,11 @@
       <c r="W246" t="n">
         <v>-1</v>
       </c>
-      <c r="X246" t="b">
-        <v>1</v>
+      <c r="X246" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -20852,8 +21592,11 @@
       <c r="W247" t="n">
         <v>-1</v>
       </c>
-      <c r="X247" t="b">
-        <v>1</v>
+      <c r="X247" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -20936,8 +21679,11 @@
       <c r="W248" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X248" t="b">
-        <v>1</v>
+      <c r="X248" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -21020,8 +21766,11 @@
       <c r="W249" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X249" t="b">
-        <v>1</v>
+      <c r="X249" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -21102,8 +21851,11 @@
       <c r="W250" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X250" t="b">
-        <v>1</v>
+      <c r="X250" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -21184,7 +21936,10 @@
       <c r="W251" t="n">
         <v>-1</v>
       </c>
-      <c r="X251" t="b">
+      <c r="X251" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y251" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21266,8 +22021,11 @@
       <c r="W252" t="n">
         <v>1</v>
       </c>
-      <c r="X252" t="b">
-        <v>1</v>
+      <c r="X252" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -21350,8 +22108,11 @@
       <c r="W253" t="n">
         <v>-1</v>
       </c>
-      <c r="X253" t="b">
-        <v>0</v>
+      <c r="X253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -21434,8 +22195,11 @@
       <c r="W254" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X254" t="b">
-        <v>0</v>
+      <c r="X254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -21516,8 +22280,11 @@
       <c r="W255" t="n">
         <v>-1</v>
       </c>
-      <c r="X255" t="b">
-        <v>1</v>
+      <c r="X255" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -21598,7 +22365,10 @@
       <c r="W256" t="n">
         <v>-1</v>
       </c>
-      <c r="X256" t="b">
+      <c r="X256" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y256" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21680,8 +22450,11 @@
       <c r="W257" t="n">
         <v>-1</v>
       </c>
-      <c r="X257" t="b">
-        <v>0</v>
+      <c r="X257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -21762,7 +22535,10 @@
       <c r="W258" t="n">
         <v>-1</v>
       </c>
-      <c r="X258" t="b">
+      <c r="X258" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y258" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21844,8 +22620,11 @@
       <c r="W259" t="n">
         <v>-1</v>
       </c>
-      <c r="X259" t="b">
-        <v>1</v>
+      <c r="X259" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -21926,8 +22705,11 @@
       <c r="W260" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X260" t="b">
-        <v>1</v>
+      <c r="X260" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -22010,7 +22792,10 @@
       <c r="W261" t="n">
         <v>-1</v>
       </c>
-      <c r="X261" t="b">
+      <c r="X261" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y261" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22092,7 +22877,10 @@
       <c r="W262" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X262" t="b">
+      <c r="X262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22174,7 +22962,10 @@
       <c r="W263" t="n">
         <v>-1</v>
       </c>
-      <c r="X263" t="b">
+      <c r="X263" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y263" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22256,7 +23047,10 @@
       <c r="W264" t="n">
         <v>-1</v>
       </c>
-      <c r="X264" t="b">
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22340,8 +23134,11 @@
       <c r="W265" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X265" t="b">
-        <v>1</v>
+      <c r="X265" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -22422,7 +23219,10 @@
       <c r="W266" t="n">
         <v>-1</v>
       </c>
-      <c r="X266" t="b">
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22504,8 +23304,11 @@
       <c r="W267" t="n">
         <v>-1</v>
       </c>
-      <c r="X267" t="b">
-        <v>0</v>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -22586,7 +23389,10 @@
       <c r="W268" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X268" t="b">
+      <c r="X268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22668,8 +23474,11 @@
       <c r="W269" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X269" t="b">
-        <v>0</v>
+      <c r="X269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -22750,8 +23559,11 @@
       <c r="W270" t="n">
         <v>-1</v>
       </c>
-      <c r="X270" t="b">
-        <v>1</v>
+      <c r="X270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -22834,8 +23646,11 @@
       <c r="W271" t="n">
         <v>1</v>
       </c>
-      <c r="X271" t="b">
-        <v>0</v>
+      <c r="X271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -22916,8 +23731,11 @@
       <c r="W272" t="n">
         <v>-1</v>
       </c>
-      <c r="X272" t="b">
-        <v>0</v>
+      <c r="X272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -23000,7 +23818,10 @@
       <c r="W273" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X273" t="b">
+      <c r="X273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23082,7 +23903,10 @@
       <c r="W274" t="n">
         <v>1</v>
       </c>
-      <c r="X274" t="b">
+      <c r="X274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23164,8 +23988,11 @@
       <c r="W275" t="n">
         <v>-0.7071067811865477</v>
       </c>
-      <c r="X275" t="b">
-        <v>1</v>
+      <c r="X275" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -23246,7 +24073,10 @@
       <c r="W276" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X276" t="b">
+      <c r="X276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23328,8 +24158,11 @@
       <c r="W277" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X277" t="b">
-        <v>0</v>
+      <c r="X277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -23412,8 +24245,11 @@
       <c r="W278" t="n">
         <v>-0.7071067811865475</v>
       </c>
-      <c r="X278" t="b">
-        <v>0</v>
+      <c r="X278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -23494,7 +24330,10 @@
       <c r="W279" t="n">
         <v>-1</v>
       </c>
-      <c r="X279" t="b">
+      <c r="X279" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y279" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23578,8 +24417,11 @@
       <c r="W280" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X280" t="b">
-        <v>0</v>
+      <c r="X280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -23660,8 +24502,11 @@
       <c r="W281" t="n">
         <v>-1</v>
       </c>
-      <c r="X281" t="b">
-        <v>0</v>
+      <c r="X281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -23742,8 +24587,11 @@
       <c r="W282" t="n">
         <v>-1</v>
       </c>
-      <c r="X282" t="b">
-        <v>1</v>
+      <c r="X282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -23824,8 +24672,11 @@
       <c r="W283" t="n">
         <v>-1</v>
       </c>
-      <c r="X283" t="b">
-        <v>0</v>
+      <c r="X283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -23906,7 +24757,10 @@
       <c r="W284" t="n">
         <v>-1</v>
       </c>
-      <c r="X284" t="b">
+      <c r="X284" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y284" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23988,7 +24842,10 @@
       <c r="W285" t="n">
         <v>1</v>
       </c>
-      <c r="X285" t="b">
+      <c r="X285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24070,8 +24927,11 @@
       <c r="W286" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X286" t="b">
-        <v>0</v>
+      <c r="X286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -24152,7 +25012,10 @@
       <c r="W287" t="n">
         <v>-1</v>
       </c>
-      <c r="X287" t="b">
+      <c r="X287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24236,8 +25099,11 @@
       <c r="W288" t="n">
         <v>0.7071067811865476</v>
       </c>
-      <c r="X288" t="b">
-        <v>1</v>
+      <c r="X288" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -24320,8 +25186,11 @@
       <c r="W289" t="n">
         <v>-1</v>
       </c>
-      <c r="X289" t="b">
-        <v>0</v>
+      <c r="X289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -24402,8 +25271,11 @@
       <c r="W290" t="n">
         <v>-1</v>
       </c>
-      <c r="X290" t="b">
-        <v>0</v>
+      <c r="X290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -24484,8 +25356,11 @@
       <c r="W291" t="n">
         <v>-1</v>
       </c>
-      <c r="X291" t="b">
-        <v>0</v>
+      <c r="X291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -24568,8 +25443,11 @@
       <c r="W292" t="n">
         <v>-0.9238795325112865</v>
       </c>
-      <c r="X292" t="b">
-        <v>1</v>
+      <c r="X292" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -24650,8 +25528,11 @@
       <c r="W293" t="n">
         <v>-1</v>
       </c>
-      <c r="X293" t="b">
-        <v>0</v>
+      <c r="X293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -24732,7 +25613,10 @@
       <c r="W294" t="n">
         <v>-1</v>
       </c>
-      <c r="X294" t="b">
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="n">
         <v>0</v>
       </c>
     </row>
